--- a/research/traditional_assets/database/data/zambia/zambia_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_construction_supplies.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1627885951062328</v>
+        <v>0.1622480850233609</v>
       </c>
       <c r="C2">
-        <v>182.4</v>
+        <v>181.3144849151246</v>
       </c>
       <c r="D2">
-        <v>159.1</v>
+        <v>159.8384849151246</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.824</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.824</v>
       </c>
       <c r="G2">
         <v>23.3</v>
@@ -1451,28 +1451,28 @@
         <v>18.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0917472</v>
       </c>
       <c r="N2">
-        <v>18.8</v>
+        <v>18.7082528</v>
       </c>
       <c r="O2">
-        <v>6.58</v>
+        <v>6.54788848</v>
       </c>
       <c r="P2">
-        <v>12.22</v>
+        <v>12.16036432</v>
       </c>
       <c r="Q2">
-        <v>15.12</v>
+        <v>15.06036432</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1627885951062328</v>
+        <v>0.1635567020437989</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7201853307896295</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.9108855638101</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1622480850233609</v>
+        <v>0.1617075749404891</v>
       </c>
       <c r="C3">
-        <v>181.3144849151246</v>
+        <v>180.2358573618516</v>
       </c>
       <c r="D3">
-        <v>159.8384849151246</v>
+        <v>160.5838573618516</v>
       </c>
       <c r="E3">
-        <v>1.824</v>
+        <v>3.648</v>
       </c>
       <c r="F3">
-        <v>1.824</v>
+        <v>3.648</v>
       </c>
       <c r="G3">
         <v>23.3</v>
@@ -1533,28 +1533,28 @@
         <v>18.8</v>
       </c>
       <c r="M3">
-        <v>0.0917472</v>
+        <v>0.1834944</v>
       </c>
       <c r="N3">
-        <v>18.7082528</v>
+        <v>18.6165056</v>
       </c>
       <c r="O3">
-        <v>6.54788848</v>
+        <v>6.515776959999999</v>
       </c>
       <c r="P3">
-        <v>12.16036432</v>
+        <v>12.10072864</v>
       </c>
       <c r="Q3">
-        <v>15.06036432</v>
+        <v>15.00072864</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1635567020437989</v>
+        <v>0.1643404846331522</v>
       </c>
       <c r="T3">
-        <v>0.7201853307896295</v>
+        <v>0.7249788475371567</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.9108855638101</v>
+        <v>102.4554427819051</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1617075749404891</v>
+        <v>0.1611670648576173</v>
       </c>
       <c r="C4">
-        <v>180.2358573618516</v>
+        <v>179.1642141471928</v>
       </c>
       <c r="D4">
-        <v>160.5838573618516</v>
+        <v>161.3362141471928</v>
       </c>
       <c r="E4">
-        <v>3.648</v>
+        <v>5.472</v>
       </c>
       <c r="F4">
-        <v>3.648</v>
+        <v>5.472</v>
       </c>
       <c r="G4">
         <v>23.3</v>
@@ -1615,28 +1615,28 @@
         <v>18.8</v>
       </c>
       <c r="M4">
-        <v>0.1834944</v>
+        <v>0.2752416</v>
       </c>
       <c r="N4">
-        <v>18.6165056</v>
+        <v>18.5247584</v>
       </c>
       <c r="O4">
-        <v>6.515776959999999</v>
+        <v>6.483665439999999</v>
       </c>
       <c r="P4">
-        <v>12.10072864</v>
+        <v>12.04109296</v>
       </c>
       <c r="Q4">
-        <v>15.00072864</v>
+        <v>14.94109296</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1643404846331522</v>
+        <v>0.1651404276882653</v>
       </c>
       <c r="T4">
-        <v>0.7249788475371567</v>
+        <v>0.72987119968154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.4554427819051</v>
+        <v>68.30362852127004</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1611670648576173</v>
+        <v>0.1606265547747455</v>
       </c>
       <c r="C5">
-        <v>179.1642141471928</v>
+        <v>178.0996539009153</v>
       </c>
       <c r="D5">
-        <v>161.3362141471928</v>
+        <v>162.0956539009152</v>
       </c>
       <c r="E5">
-        <v>5.472</v>
+        <v>7.296</v>
       </c>
       <c r="F5">
-        <v>5.472</v>
+        <v>7.296</v>
       </c>
       <c r="G5">
         <v>23.3</v>
@@ -1697,28 +1697,28 @@
         <v>18.8</v>
       </c>
       <c r="M5">
-        <v>0.2752416</v>
+        <v>0.3669888</v>
       </c>
       <c r="N5">
-        <v>18.5247584</v>
+        <v>18.4330112</v>
       </c>
       <c r="O5">
-        <v>6.483665439999999</v>
+        <v>6.451553919999999</v>
       </c>
       <c r="P5">
-        <v>12.04109296</v>
+        <v>11.98145728</v>
       </c>
       <c r="Q5">
-        <v>14.94109296</v>
+        <v>14.88145728</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1651404276882653</v>
+        <v>0.1659570362236932</v>
       </c>
       <c r="T5">
-        <v>0.72987119968154</v>
+        <v>0.7348654758289315</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.30362852127004</v>
+        <v>51.22772139095252</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1606265547747455</v>
+        <v>0.1600860446918737</v>
       </c>
       <c r="C6">
-        <v>178.0996539009153</v>
+        <v>177.0422771186437</v>
       </c>
       <c r="D6">
-        <v>162.0956539009152</v>
+        <v>162.8622771186437</v>
       </c>
       <c r="E6">
-        <v>7.296</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="F6">
-        <v>7.296</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="G6">
         <v>23.3</v>
@@ -1779,28 +1779,28 @@
         <v>18.8</v>
       </c>
       <c r="M6">
-        <v>0.3669888</v>
+        <v>0.458736</v>
       </c>
       <c r="N6">
-        <v>18.4330112</v>
+        <v>18.341264</v>
       </c>
       <c r="O6">
-        <v>6.451553919999999</v>
+        <v>6.4194424</v>
       </c>
       <c r="P6">
-        <v>11.98145728</v>
+        <v>11.9218216</v>
       </c>
       <c r="Q6">
-        <v>14.88145728</v>
+        <v>14.8218216</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1659570362236932</v>
+        <v>0.1667908365177618</v>
       </c>
       <c r="T6">
-        <v>0.7348654758289315</v>
+        <v>0.7399648946320574</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.22772139095252</v>
+        <v>40.98217711276202</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1600860446918737</v>
+        <v>0.1595455346090019</v>
       </c>
       <c r="C7">
-        <v>177.0422771186437</v>
+        <v>175.9921862061933</v>
       </c>
       <c r="D7">
-        <v>162.8622771186437</v>
+        <v>163.6361862061933</v>
       </c>
       <c r="E7">
-        <v>9.120000000000001</v>
+        <v>10.944</v>
       </c>
       <c r="F7">
-        <v>9.120000000000001</v>
+        <v>10.944</v>
       </c>
       <c r="G7">
         <v>23.3</v>
@@ -1861,28 +1861,28 @@
         <v>18.8</v>
       </c>
       <c r="M7">
-        <v>0.458736</v>
+        <v>0.5504832000000001</v>
       </c>
       <c r="N7">
-        <v>18.341264</v>
+        <v>18.2495168</v>
       </c>
       <c r="O7">
-        <v>6.4194424</v>
+        <v>6.38733088</v>
       </c>
       <c r="P7">
-        <v>11.9218216</v>
+        <v>11.86218592</v>
       </c>
       <c r="Q7">
-        <v>14.8218216</v>
+        <v>14.76218592</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1667908365177618</v>
+        <v>0.167642377243619</v>
       </c>
       <c r="T7">
-        <v>0.7399648946320574</v>
+        <v>0.7451728117075902</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.98217711276202</v>
+        <v>34.15181426063502</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1595455346090019</v>
+        <v>0.1590050245261301</v>
       </c>
       <c r="C8">
-        <v>175.9921862061933</v>
+        <v>174.9494855251711</v>
       </c>
       <c r="D8">
-        <v>163.6361862061933</v>
+        <v>164.4174855251711</v>
       </c>
       <c r="E8">
-        <v>10.944</v>
+        <v>12.768</v>
       </c>
       <c r="F8">
-        <v>10.944</v>
+        <v>12.768</v>
       </c>
       <c r="G8">
         <v>23.3</v>
@@ -1943,28 +1943,28 @@
         <v>18.8</v>
       </c>
       <c r="M8">
-        <v>0.5504832</v>
+        <v>0.6422303999999999</v>
       </c>
       <c r="N8">
-        <v>18.2495168</v>
+        <v>18.1577696</v>
       </c>
       <c r="O8">
-        <v>6.38733088</v>
+        <v>6.35521936</v>
       </c>
       <c r="P8">
-        <v>11.86218592</v>
+        <v>11.80255024</v>
       </c>
       <c r="Q8">
-        <v>14.76218592</v>
+        <v>14.70255024</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.167642377243619</v>
+        <v>0.1685122306732581</v>
       </c>
       <c r="T8">
-        <v>0.7451728117075902</v>
+        <v>0.7504927269998011</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.15181426063503</v>
+        <v>29.27298365197288</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.15900502452613</v>
+        <v>0.1584645144432582</v>
       </c>
       <c r="C9">
-        <v>174.9494855251712</v>
+        <v>173.9142814398915</v>
       </c>
       <c r="D9">
-        <v>164.4174855251712</v>
+        <v>165.2062814398915</v>
       </c>
       <c r="E9">
-        <v>12.768</v>
+        <v>14.592</v>
       </c>
       <c r="F9">
-        <v>12.768</v>
+        <v>14.592</v>
       </c>
       <c r="G9">
         <v>23.3</v>
@@ -2025,28 +2025,28 @@
         <v>18.8</v>
       </c>
       <c r="M9">
-        <v>0.6422304000000001</v>
+        <v>0.7339776</v>
       </c>
       <c r="N9">
-        <v>18.1577696</v>
+        <v>18.0660224</v>
       </c>
       <c r="O9">
-        <v>6.35521936</v>
+        <v>6.32310784</v>
       </c>
       <c r="P9">
-        <v>11.80255024</v>
+        <v>11.74291456</v>
       </c>
       <c r="Q9">
-        <v>14.70255024</v>
+        <v>14.64291456</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1685122306732581</v>
+        <v>0.1694009939600633</v>
       </c>
       <c r="T9">
-        <v>0.7504927269998011</v>
+        <v>0.7559282926244515</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.27298365197287</v>
+        <v>25.61386069547627</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1584645144432582</v>
+        <v>0.1579240043603864</v>
       </c>
       <c r="C10">
-        <v>173.9142814398915</v>
+        <v>172.8866823656469</v>
       </c>
       <c r="D10">
-        <v>165.2062814398915</v>
+        <v>166.0026823656468</v>
       </c>
       <c r="E10">
-        <v>14.592</v>
+        <v>16.416</v>
       </c>
       <c r="F10">
-        <v>14.592</v>
+        <v>16.416</v>
       </c>
       <c r="G10">
         <v>23.3</v>
@@ -2107,28 +2107,28 @@
         <v>18.8</v>
       </c>
       <c r="M10">
-        <v>0.7339776</v>
+        <v>0.8257247999999999</v>
       </c>
       <c r="N10">
-        <v>18.0660224</v>
+        <v>17.9742752</v>
       </c>
       <c r="O10">
-        <v>6.32310784</v>
+        <v>6.29099632</v>
       </c>
       <c r="P10">
-        <v>11.74291456</v>
+        <v>11.68327888</v>
       </c>
       <c r="Q10">
-        <v>14.64291456</v>
+        <v>14.58327888</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1694009939600633</v>
+        <v>0.1703092905059191</v>
       </c>
       <c r="T10">
-        <v>0.7559282926244515</v>
+        <v>0.7614833212298634</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.61386069547627</v>
+        <v>22.76787617375668</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1579240043603864</v>
+        <v>0.1573834942775146</v>
       </c>
       <c r="C11">
-        <v>172.8866823656469</v>
+        <v>171.8667988183835</v>
       </c>
       <c r="D11">
-        <v>166.0026823656468</v>
+        <v>166.8067988183835</v>
       </c>
       <c r="E11">
-        <v>16.416</v>
+        <v>18.24</v>
       </c>
       <c r="F11">
-        <v>16.416</v>
+        <v>18.24</v>
       </c>
       <c r="G11">
         <v>23.3</v>
@@ -2189,28 +2189,28 @@
         <v>18.8</v>
       </c>
       <c r="M11">
-        <v>0.8257247999999999</v>
+        <v>0.9174719999999998</v>
       </c>
       <c r="N11">
-        <v>17.9742752</v>
+        <v>17.882528</v>
       </c>
       <c r="O11">
-        <v>6.29099632</v>
+        <v>6.2588848</v>
       </c>
       <c r="P11">
-        <v>11.68327888</v>
+        <v>11.6236432</v>
       </c>
       <c r="Q11">
-        <v>14.58327888</v>
+        <v>14.5236432</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1703092905059191</v>
+        <v>0.1712377714194607</v>
       </c>
       <c r="T11">
-        <v>0.7614833212298634</v>
+        <v>0.7671617949153956</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.76787617375668</v>
+        <v>20.49108855638102</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1573834942775146</v>
+        <v>0.1568429841946428</v>
       </c>
       <c r="C12">
-        <v>171.8667988183835</v>
+        <v>170.8547434658262</v>
       </c>
       <c r="D12">
-        <v>166.8067988183835</v>
+        <v>167.6187434658262</v>
       </c>
       <c r="E12">
-        <v>18.24</v>
+        <v>20.064</v>
       </c>
       <c r="F12">
-        <v>18.24</v>
+        <v>20.064</v>
       </c>
       <c r="G12">
         <v>23.3</v>
@@ -2271,28 +2271,28 @@
         <v>18.8</v>
       </c>
       <c r="M12">
-        <v>0.9174720000000001</v>
+        <v>1.0092192</v>
       </c>
       <c r="N12">
-        <v>17.882528</v>
+        <v>17.7907808</v>
       </c>
       <c r="O12">
-        <v>6.2588848</v>
+        <v>6.22677328</v>
       </c>
       <c r="P12">
-        <v>11.6236432</v>
+        <v>11.56400752</v>
       </c>
       <c r="Q12">
-        <v>14.5236432</v>
+        <v>14.46400752</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1712377714194607</v>
+        <v>0.1721871170726324</v>
       </c>
       <c r="T12">
-        <v>0.7671617949153956</v>
+        <v>0.7729678747511646</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.49108855638101</v>
+        <v>18.62826232398274</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1568429841946428</v>
+        <v>0.156302474111771</v>
       </c>
       <c r="C13">
-        <v>170.8547434658262</v>
+        <v>169.8506311801045</v>
       </c>
       <c r="D13">
-        <v>167.6187434658262</v>
+        <v>168.4386311801045</v>
       </c>
       <c r="E13">
-        <v>20.064</v>
+        <v>21.888</v>
       </c>
       <c r="F13">
-        <v>20.064</v>
+        <v>21.888</v>
       </c>
       <c r="G13">
         <v>23.3</v>
@@ -2353,28 +2353,28 @@
         <v>18.8</v>
       </c>
       <c r="M13">
-        <v>1.0092192</v>
+        <v>1.1009664</v>
       </c>
       <c r="N13">
-        <v>17.7907808</v>
+        <v>17.6990336</v>
       </c>
       <c r="O13">
-        <v>6.22677328</v>
+        <v>6.19466176</v>
       </c>
       <c r="P13">
-        <v>11.56400752</v>
+        <v>11.50437184</v>
       </c>
       <c r="Q13">
-        <v>14.46400752</v>
+        <v>14.40437184</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1721871170726324</v>
+        <v>0.1731580387633761</v>
       </c>
       <c r="T13">
-        <v>0.7729678747511646</v>
+        <v>0.7789059109468371</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.62826232398274</v>
+        <v>17.07590713031751</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.156302474111771</v>
+        <v>0.1557619640288991</v>
       </c>
       <c r="C14">
-        <v>169.8506311801045</v>
+        <v>168.8545790919301</v>
       </c>
       <c r="D14">
-        <v>168.4386311801045</v>
+        <v>169.2665790919301</v>
       </c>
       <c r="E14">
-        <v>21.888</v>
+        <v>23.712</v>
       </c>
       <c r="F14">
-        <v>21.888</v>
+        <v>23.712</v>
       </c>
       <c r="G14">
         <v>23.3</v>
@@ -2435,28 +2435,28 @@
         <v>18.8</v>
       </c>
       <c r="M14">
-        <v>1.1009664</v>
+        <v>1.1927136</v>
       </c>
       <c r="N14">
-        <v>17.6990336</v>
+        <v>17.6072864</v>
       </c>
       <c r="O14">
-        <v>6.19466176</v>
+        <v>6.16255024</v>
       </c>
       <c r="P14">
-        <v>11.50437184</v>
+        <v>11.44473616</v>
       </c>
       <c r="Q14">
-        <v>14.40437184</v>
+        <v>14.34473616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1731580387633761</v>
+        <v>0.1741512804929875</v>
       </c>
       <c r="T14">
-        <v>0.7789059109468371</v>
+        <v>0.7849804537217207</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.07590713031751</v>
+        <v>15.76237581260078</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1557619640288991</v>
+        <v>0.1552214539460273</v>
       </c>
       <c r="C15">
-        <v>168.8545790919301</v>
+        <v>167.8667066463815</v>
       </c>
       <c r="D15">
-        <v>169.2665790919301</v>
+        <v>170.1027066463815</v>
       </c>
       <c r="E15">
-        <v>23.712</v>
+        <v>25.536</v>
       </c>
       <c r="F15">
-        <v>23.712</v>
+        <v>25.536</v>
       </c>
       <c r="G15">
         <v>23.3</v>
@@ -2517,28 +2517,28 @@
         <v>18.8</v>
       </c>
       <c r="M15">
-        <v>1.1927136</v>
+        <v>1.2844608</v>
       </c>
       <c r="N15">
-        <v>17.6072864</v>
+        <v>17.5155392</v>
       </c>
       <c r="O15">
-        <v>6.16255024</v>
+        <v>6.130438719999999</v>
       </c>
       <c r="P15">
-        <v>11.44473616</v>
+        <v>11.38510048</v>
       </c>
       <c r="Q15">
-        <v>14.34473616</v>
+        <v>14.28510048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1741512804929875</v>
+        <v>0.1751676208674737</v>
       </c>
       <c r="T15">
-        <v>0.7849804537217207</v>
+        <v>0.7911962649332295</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.76237581260078</v>
+        <v>14.63649182598643</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1552214539460273</v>
+        <v>0.1546809438631555</v>
       </c>
       <c r="C16">
-        <v>167.8667066463815</v>
+        <v>166.8871356603484</v>
       </c>
       <c r="D16">
-        <v>170.1027066463815</v>
+        <v>170.9471356603484</v>
       </c>
       <c r="E16">
-        <v>25.536</v>
+        <v>27.36000000000001</v>
       </c>
       <c r="F16">
-        <v>25.536</v>
+        <v>27.36000000000001</v>
       </c>
       <c r="G16">
         <v>23.3</v>
@@ -2599,28 +2599,28 @@
         <v>18.8</v>
       </c>
       <c r="M16">
-        <v>1.2844608</v>
+        <v>1.376208</v>
       </c>
       <c r="N16">
-        <v>17.5155392</v>
+        <v>17.423792</v>
       </c>
       <c r="O16">
-        <v>6.130438719999999</v>
+        <v>6.098327199999999</v>
       </c>
       <c r="P16">
-        <v>11.38510048</v>
+        <v>11.3254648</v>
       </c>
       <c r="Q16">
-        <v>14.28510048</v>
+        <v>14.2254648</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1751676208674737</v>
+        <v>0.1762078751331242</v>
       </c>
       <c r="T16">
-        <v>0.7911962649332295</v>
+        <v>0.7975583305261855</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.63649182598643</v>
+        <v>13.660725704254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1546809438631555</v>
+        <v>0.1542964337802837</v>
       </c>
       <c r="C17">
-        <v>166.8871356603485</v>
+        <v>165.6689702948082</v>
       </c>
       <c r="D17">
-        <v>170.9471356603484</v>
+        <v>171.5529702948081</v>
       </c>
       <c r="E17">
-        <v>27.36</v>
+        <v>29.184</v>
       </c>
       <c r="F17">
-        <v>27.36</v>
+        <v>29.184</v>
       </c>
       <c r="G17">
         <v>23.3</v>
@@ -2681,45 +2681,45 @@
         <v>18.8</v>
       </c>
       <c r="M17">
-        <v>1.376208</v>
+        <v>1.5117312</v>
       </c>
       <c r="N17">
-        <v>17.423792</v>
+        <v>17.2882688</v>
       </c>
       <c r="O17">
-        <v>6.098327200000001</v>
+        <v>6.05089408</v>
       </c>
       <c r="P17">
-        <v>11.3254648</v>
+        <v>11.23737472</v>
       </c>
       <c r="Q17">
-        <v>14.2254648</v>
+        <v>14.13737472</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1762078751331242</v>
+        <v>0.1772728973574806</v>
       </c>
       <c r="T17">
-        <v>0.7975583305261855</v>
+        <v>0.8040718738713547</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.66072570425401</v>
+        <v>12.43607329133645</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1542964337802837</v>
+        <v>0.1537656736974119</v>
       </c>
       <c r="C18">
-        <v>165.6689702948082</v>
+        <v>164.6883260171627</v>
       </c>
       <c r="D18">
-        <v>171.5529702948081</v>
+        <v>172.3963260171627</v>
       </c>
       <c r="E18">
-        <v>29.184</v>
+        <v>31.008</v>
       </c>
       <c r="F18">
-        <v>29.184</v>
+        <v>31.008</v>
       </c>
       <c r="G18">
         <v>23.3</v>
@@ -2763,28 +2763,28 @@
         <v>18.8</v>
       </c>
       <c r="M18">
-        <v>1.5117312</v>
+        <v>1.6062144</v>
       </c>
       <c r="N18">
-        <v>17.2882688</v>
+        <v>17.1937856</v>
       </c>
       <c r="O18">
-        <v>6.05089408</v>
+        <v>6.01782496</v>
       </c>
       <c r="P18">
-        <v>11.23737472</v>
+        <v>11.17596064</v>
       </c>
       <c r="Q18">
-        <v>14.13737472</v>
+        <v>14.07596064</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1772728973574806</v>
+        <v>0.1783635827679662</v>
       </c>
       <c r="T18">
-        <v>0.8040718738713547</v>
+        <v>0.8107423700682148</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.43607329133645</v>
+        <v>11.70453956831666</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1537656736974119</v>
+        <v>0.1532349136145401</v>
       </c>
       <c r="C19">
-        <v>164.6883260171627</v>
+        <v>163.7160145903202</v>
       </c>
       <c r="D19">
-        <v>172.3963260171627</v>
+        <v>173.2480145903203</v>
       </c>
       <c r="E19">
-        <v>31.008</v>
+        <v>32.83200000000001</v>
       </c>
       <c r="F19">
-        <v>31.008</v>
+        <v>32.83200000000001</v>
       </c>
       <c r="G19">
         <v>23.3</v>
@@ -2845,28 +2845,28 @@
         <v>18.8</v>
       </c>
       <c r="M19">
-        <v>1.6062144</v>
+        <v>1.7006976</v>
       </c>
       <c r="N19">
-        <v>17.1937856</v>
+        <v>17.0993024</v>
       </c>
       <c r="O19">
-        <v>6.01782496</v>
+        <v>5.984755839999999</v>
       </c>
       <c r="P19">
-        <v>11.17596064</v>
+        <v>11.11454656</v>
       </c>
       <c r="Q19">
-        <v>14.07596064</v>
+        <v>14.01454656</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1783635827679662</v>
+        <v>0.1794808702616342</v>
       </c>
       <c r="T19">
-        <v>0.8107423700682148</v>
+        <v>0.8175755612942665</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.70453956831666</v>
+        <v>11.05428737007684</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1532349136145401</v>
+        <v>0.1527041535316683</v>
       </c>
       <c r="C20">
-        <v>163.7160145903202</v>
+        <v>162.7521601276411</v>
       </c>
       <c r="D20">
-        <v>173.2480145903202</v>
+        <v>174.1081601276411</v>
       </c>
       <c r="E20">
-        <v>32.832</v>
+        <v>34.656</v>
       </c>
       <c r="F20">
-        <v>32.832</v>
+        <v>34.656</v>
       </c>
       <c r="G20">
         <v>23.3</v>
@@ -2927,28 +2927,28 @@
         <v>18.8</v>
       </c>
       <c r="M20">
-        <v>1.7006976</v>
+        <v>1.7951808</v>
       </c>
       <c r="N20">
-        <v>17.0993024</v>
+        <v>17.0048192</v>
       </c>
       <c r="O20">
-        <v>5.984755839999999</v>
+        <v>5.95168672</v>
       </c>
       <c r="P20">
-        <v>11.11454656</v>
+        <v>11.05313248</v>
       </c>
       <c r="Q20">
-        <v>14.01454656</v>
+        <v>13.95313248</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1794808702616342</v>
+        <v>0.180625745100825</v>
       </c>
       <c r="T20">
-        <v>0.8175755612942665</v>
+        <v>0.824577473291332</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.05428737007684</v>
+        <v>10.47248277165175</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1527041535316683</v>
+        <v>0.1521733934487965</v>
       </c>
       <c r="C21">
-        <v>162.7521601276411</v>
+        <v>161.7968892195873</v>
       </c>
       <c r="D21">
-        <v>174.1081601276411</v>
+        <v>174.9768892195873</v>
       </c>
       <c r="E21">
-        <v>34.656</v>
+        <v>36.48</v>
       </c>
       <c r="F21">
-        <v>34.656</v>
+        <v>36.48</v>
       </c>
       <c r="G21">
         <v>23.3</v>
@@ -3009,28 +3009,28 @@
         <v>18.8</v>
       </c>
       <c r="M21">
-        <v>1.7951808</v>
+        <v>1.889664</v>
       </c>
       <c r="N21">
-        <v>17.0048192</v>
+        <v>16.910336</v>
       </c>
       <c r="O21">
-        <v>5.95168672</v>
+        <v>5.9186176</v>
       </c>
       <c r="P21">
-        <v>11.05313248</v>
+        <v>10.9917184</v>
       </c>
       <c r="Q21">
-        <v>13.95313248</v>
+        <v>13.8917184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.180625745100825</v>
+        <v>0.1817992418109956</v>
       </c>
       <c r="T21">
-        <v>0.824577473291332</v>
+        <v>0.8317544330883241</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.47248277165175</v>
+        <v>9.948858633069159</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1521733934487965</v>
+        <v>0.1518746833659247</v>
       </c>
       <c r="C22">
-        <v>161.7968892195873</v>
+        <v>160.4656303659278</v>
       </c>
       <c r="D22">
-        <v>174.9768892195873</v>
+        <v>175.4696303659278</v>
       </c>
       <c r="E22">
-        <v>36.48</v>
+        <v>38.304</v>
       </c>
       <c r="F22">
-        <v>36.48</v>
+        <v>38.304</v>
       </c>
       <c r="G22">
         <v>23.3</v>
@@ -3091,45 +3091,45 @@
         <v>18.8</v>
       </c>
       <c r="M22">
-        <v>1.889664</v>
+        <v>2.049264</v>
       </c>
       <c r="N22">
-        <v>16.910336</v>
+        <v>16.750736</v>
       </c>
       <c r="O22">
-        <v>5.9186176</v>
+        <v>5.862757599999999</v>
       </c>
       <c r="P22">
-        <v>10.9917184</v>
+        <v>10.8879784</v>
       </c>
       <c r="Q22">
-        <v>13.8917184</v>
+        <v>13.7879784</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1817992418109956</v>
+        <v>0.1830024472986388</v>
       </c>
       <c r="T22">
-        <v>0.8317544330883241</v>
+        <v>0.83911308807005</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.948858633069159</v>
+        <v>9.174025406194614</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1518746833659247</v>
+        <v>0.1513549732830528</v>
       </c>
       <c r="C23">
-        <v>160.4656303659278</v>
+        <v>159.5055720003444</v>
       </c>
       <c r="D23">
-        <v>175.4696303659278</v>
+        <v>176.3335720003444</v>
       </c>
       <c r="E23">
-        <v>38.304</v>
+        <v>40.128</v>
       </c>
       <c r="F23">
-        <v>38.304</v>
+        <v>40.128</v>
       </c>
       <c r="G23">
         <v>23.3</v>
@@ -3173,28 +3173,28 @@
         <v>18.8</v>
       </c>
       <c r="M23">
-        <v>2.049264</v>
+        <v>2.146848</v>
       </c>
       <c r="N23">
-        <v>16.750736</v>
+        <v>16.653152</v>
       </c>
       <c r="O23">
-        <v>5.862757599999999</v>
+        <v>5.828603200000001</v>
       </c>
       <c r="P23">
-        <v>10.8879784</v>
+        <v>10.8245488</v>
       </c>
       <c r="Q23">
-        <v>13.7879784</v>
+        <v>13.7245488</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1830024472986388</v>
+        <v>0.1842365042090421</v>
       </c>
       <c r="T23">
-        <v>0.83911308807005</v>
+        <v>0.8466604265128459</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.174025406194614</v>
+        <v>8.757024251367588</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1513549732830528</v>
+        <v>0.150835263200181</v>
       </c>
       <c r="C24">
-        <v>159.5055720003444</v>
+        <v>158.5540631288022</v>
       </c>
       <c r="D24">
-        <v>176.3335720003444</v>
+        <v>177.2060631288022</v>
       </c>
       <c r="E24">
-        <v>40.128</v>
+        <v>41.95200000000001</v>
       </c>
       <c r="F24">
-        <v>40.128</v>
+        <v>41.95200000000001</v>
       </c>
       <c r="G24">
         <v>23.3</v>
@@ -3255,28 +3255,28 @@
         <v>18.8</v>
       </c>
       <c r="M24">
-        <v>2.146848</v>
+        <v>2.244432</v>
       </c>
       <c r="N24">
-        <v>16.653152</v>
+        <v>16.555568</v>
       </c>
       <c r="O24">
-        <v>5.828603200000001</v>
+        <v>5.7944488</v>
       </c>
       <c r="P24">
-        <v>10.8245488</v>
+        <v>10.7611192</v>
       </c>
       <c r="Q24">
-        <v>13.7245488</v>
+        <v>13.6611192</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1842365042090421</v>
+        <v>0.1855026145456896</v>
       </c>
       <c r="T24">
-        <v>0.8466604265128459</v>
+        <v>0.8544037997203898</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.757024251367588</v>
+        <v>8.376284066525518</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.150835263200181</v>
+        <v>0.1503155531173092</v>
       </c>
       <c r="C25">
-        <v>158.5540631288022</v>
+        <v>157.6112312899724</v>
       </c>
       <c r="D25">
-        <v>177.2060631288022</v>
+        <v>178.0872312899724</v>
       </c>
       <c r="E25">
-        <v>41.95200000000001</v>
+        <v>43.776</v>
       </c>
       <c r="F25">
-        <v>41.95200000000001</v>
+        <v>43.776</v>
       </c>
       <c r="G25">
         <v>23.3</v>
@@ -3337,28 +3337,28 @@
         <v>18.8</v>
       </c>
       <c r="M25">
-        <v>2.244432</v>
+        <v>2.342016</v>
       </c>
       <c r="N25">
-        <v>16.555568</v>
+        <v>16.457984</v>
       </c>
       <c r="O25">
-        <v>5.7944488</v>
+        <v>5.760294399999999</v>
       </c>
       <c r="P25">
-        <v>10.7611192</v>
+        <v>10.6976896</v>
       </c>
       <c r="Q25">
-        <v>13.6611192</v>
+        <v>13.5976896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1855026145456896</v>
+        <v>0.1868020435754068</v>
       </c>
       <c r="T25">
-        <v>0.8544037997203898</v>
+        <v>0.8623509459070795</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.376284066525518</v>
+        <v>8.027272230420287</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1503155531173092</v>
+        <v>0.1497958430344374</v>
       </c>
       <c r="C26">
-        <v>157.6112312899724</v>
+        <v>156.6772065719792</v>
       </c>
       <c r="D26">
-        <v>178.0872312899724</v>
+        <v>178.9772065719792</v>
       </c>
       <c r="E26">
-        <v>43.776</v>
+        <v>45.6</v>
       </c>
       <c r="F26">
-        <v>43.776</v>
+        <v>45.6</v>
       </c>
       <c r="G26">
         <v>23.3</v>
@@ -3419,28 +3419,28 @@
         <v>18.8</v>
       </c>
       <c r="M26">
-        <v>2.342016</v>
+        <v>2.4396</v>
       </c>
       <c r="N26">
-        <v>16.457984</v>
+        <v>16.3604</v>
       </c>
       <c r="O26">
-        <v>5.760294399999999</v>
+        <v>5.72614</v>
       </c>
       <c r="P26">
-        <v>10.6976896</v>
+        <v>10.63426</v>
       </c>
       <c r="Q26">
-        <v>13.5976896</v>
+        <v>13.53426</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1868020435754068</v>
+        <v>0.1881361240459165</v>
       </c>
       <c r="T26">
-        <v>0.8623509459070795</v>
+        <v>0.8705100159920811</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.027272230420287</v>
+        <v>7.706181341203477</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1497958430344374</v>
+        <v>0.1494113329515656</v>
       </c>
       <c r="C27">
-        <v>156.6772065719792</v>
+        <v>155.5174055410566</v>
       </c>
       <c r="D27">
-        <v>178.9772065719792</v>
+        <v>179.6414055410566</v>
       </c>
       <c r="E27">
-        <v>45.6</v>
+        <v>47.42400000000001</v>
       </c>
       <c r="F27">
-        <v>45.6</v>
+        <v>47.42400000000001</v>
       </c>
       <c r="G27">
         <v>23.3</v>
@@ -3501,45 +3501,45 @@
         <v>18.8</v>
       </c>
       <c r="M27">
-        <v>2.4396</v>
+        <v>2.575123200000001</v>
       </c>
       <c r="N27">
-        <v>16.3604</v>
+        <v>16.2248768</v>
       </c>
       <c r="O27">
-        <v>5.72614</v>
+        <v>5.67870688</v>
       </c>
       <c r="P27">
-        <v>10.63426</v>
+        <v>10.54616992</v>
       </c>
       <c r="Q27">
-        <v>13.53426</v>
+        <v>13.44616992</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1881361240459165</v>
+        <v>0.1895062607453589</v>
       </c>
       <c r="T27">
-        <v>0.8705100159920811</v>
+        <v>0.8788896014847852</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.706181341203477</v>
+        <v>7.300621578027799</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1494113329515656</v>
+        <v>0.1488968228686938</v>
       </c>
       <c r="C28">
-        <v>155.5174055410566</v>
+        <v>154.5899153643501</v>
       </c>
       <c r="D28">
-        <v>179.6414055410566</v>
+        <v>180.5379153643501</v>
       </c>
       <c r="E28">
-        <v>47.42400000000001</v>
+        <v>49.248</v>
       </c>
       <c r="F28">
-        <v>47.42400000000001</v>
+        <v>49.248</v>
       </c>
       <c r="G28">
         <v>23.3</v>
@@ -3583,28 +3583,28 @@
         <v>18.8</v>
       </c>
       <c r="M28">
-        <v>2.575123200000001</v>
+        <v>2.6741664</v>
       </c>
       <c r="N28">
-        <v>16.2248768</v>
+        <v>16.1258336</v>
       </c>
       <c r="O28">
-        <v>5.67870688</v>
+        <v>5.644041759999999</v>
       </c>
       <c r="P28">
-        <v>10.54616992</v>
+        <v>10.48179184</v>
       </c>
       <c r="Q28">
-        <v>13.44616992</v>
+        <v>13.38179184</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1895062607453589</v>
+        <v>0.1909139354365668</v>
       </c>
       <c r="T28">
-        <v>0.8788896014847852</v>
+        <v>0.8874987646622212</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.300621578027799</v>
+        <v>7.030228186248992</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1488968228686938</v>
+        <v>0.1483823127858219</v>
       </c>
       <c r="C29">
-        <v>154.5899153643501</v>
+        <v>153.6714182261306</v>
       </c>
       <c r="D29">
-        <v>180.5379153643501</v>
+        <v>181.4434182261306</v>
       </c>
       <c r="E29">
-        <v>49.248</v>
+        <v>51.07200000000001</v>
       </c>
       <c r="F29">
-        <v>49.248</v>
+        <v>51.07200000000001</v>
       </c>
       <c r="G29">
         <v>23.3</v>
@@ -3665,28 +3665,28 @@
         <v>18.8</v>
       </c>
       <c r="M29">
-        <v>2.6741664</v>
+        <v>2.7732096</v>
       </c>
       <c r="N29">
-        <v>16.1258336</v>
+        <v>16.0267904</v>
       </c>
       <c r="O29">
-        <v>5.644041759999999</v>
+        <v>5.60937664</v>
       </c>
       <c r="P29">
-        <v>10.48179184</v>
+        <v>10.41741376</v>
       </c>
       <c r="Q29">
-        <v>13.38179184</v>
+        <v>13.31741376</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1909139354365668</v>
+        <v>0.1923607122025305</v>
       </c>
       <c r="T29">
-        <v>0.8874987646622212</v>
+        <v>0.8963470712612523</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.030228186248992</v>
+        <v>6.779148608168671</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1483823127858219</v>
+        <v>0.1478678027029501</v>
       </c>
       <c r="C30">
-        <v>153.6714182261306</v>
+        <v>152.7620501244948</v>
       </c>
       <c r="D30">
-        <v>181.4434182261306</v>
+        <v>182.3580501244948</v>
       </c>
       <c r="E30">
-        <v>51.07200000000001</v>
+        <v>52.89600000000001</v>
       </c>
       <c r="F30">
-        <v>51.07200000000001</v>
+        <v>52.89600000000001</v>
       </c>
       <c r="G30">
         <v>23.3</v>
@@ -3747,28 +3747,28 @@
         <v>18.8</v>
       </c>
       <c r="M30">
-        <v>2.7732096</v>
+        <v>2.8722528</v>
       </c>
       <c r="N30">
-        <v>16.0267904</v>
+        <v>15.9277472</v>
       </c>
       <c r="O30">
-        <v>5.60937664</v>
+        <v>5.57471152</v>
       </c>
       <c r="P30">
-        <v>10.41741376</v>
+        <v>10.35303568</v>
       </c>
       <c r="Q30">
-        <v>13.31741376</v>
+        <v>13.25303568</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1923607122025305</v>
+        <v>0.1938482432435917</v>
       </c>
       <c r="T30">
-        <v>0.8963470712612523</v>
+        <v>0.9054446259334958</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.779148608168671</v>
+        <v>6.545384863059406</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1478678027029501</v>
+        <v>0.1473532926200783</v>
       </c>
       <c r="C31">
-        <v>152.7620501244949</v>
+        <v>151.8619498136257</v>
       </c>
       <c r="D31">
-        <v>182.3580501244948</v>
+        <v>183.2819498136257</v>
       </c>
       <c r="E31">
-        <v>52.896</v>
+        <v>54.72</v>
       </c>
       <c r="F31">
-        <v>52.896</v>
+        <v>54.72</v>
       </c>
       <c r="G31">
         <v>23.3</v>
@@ -3829,28 +3829,28 @@
         <v>18.8</v>
       </c>
       <c r="M31">
-        <v>2.8722528</v>
+        <v>2.971296</v>
       </c>
       <c r="N31">
-        <v>15.9277472</v>
+        <v>15.828704</v>
       </c>
       <c r="O31">
-        <v>5.57471152</v>
+        <v>5.5400464</v>
       </c>
       <c r="P31">
-        <v>10.35303568</v>
+        <v>10.2886576</v>
       </c>
       <c r="Q31">
-        <v>13.25303568</v>
+        <v>13.1886576</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1938482432435917</v>
+        <v>0.1953782751715404</v>
       </c>
       <c r="T31">
-        <v>0.9054446259334958</v>
+        <v>0.9148021107392319</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.545384863059407</v>
+        <v>6.327205367624094</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1473532926200783</v>
+        <v>0.1468387825372065</v>
       </c>
       <c r="C32">
-        <v>151.8619498136257</v>
+        <v>150.9712588739639</v>
       </c>
       <c r="D32">
-        <v>183.2819498136257</v>
+        <v>184.2152588739639</v>
       </c>
       <c r="E32">
-        <v>54.72</v>
+        <v>56.544</v>
       </c>
       <c r="F32">
-        <v>54.72</v>
+        <v>56.544</v>
       </c>
       <c r="G32">
         <v>23.3</v>
@@ -3911,28 +3911,28 @@
         <v>18.8</v>
       </c>
       <c r="M32">
-        <v>2.971296</v>
+        <v>3.0703392</v>
       </c>
       <c r="N32">
-        <v>15.828704</v>
+        <v>15.7296608</v>
       </c>
       <c r="O32">
-        <v>5.5400464</v>
+        <v>5.50538128</v>
       </c>
       <c r="P32">
-        <v>10.2886576</v>
+        <v>10.22427952</v>
       </c>
       <c r="Q32">
-        <v>13.1886576</v>
+        <v>13.12427952</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1953782751715404</v>
+        <v>0.1969526558510239</v>
       </c>
       <c r="T32">
-        <v>0.9148021107392319</v>
+        <v>0.9244308269886126</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.327205367624094</v>
+        <v>6.123101968668478</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1468387825372065</v>
+        <v>0.1465322724543347</v>
       </c>
       <c r="C33">
-        <v>150.9712588739639</v>
+        <v>149.7077925826549</v>
       </c>
       <c r="D33">
-        <v>184.2152588739639</v>
+        <v>184.7757925826549</v>
       </c>
       <c r="E33">
-        <v>56.544</v>
+        <v>58.368</v>
       </c>
       <c r="F33">
-        <v>56.544</v>
+        <v>58.368</v>
       </c>
       <c r="G33">
         <v>23.3</v>
@@ -3993,45 +3993,45 @@
         <v>18.8</v>
       </c>
       <c r="M33">
-        <v>3.0703392</v>
+        <v>3.2277504</v>
       </c>
       <c r="N33">
-        <v>15.7296608</v>
+        <v>15.5722496</v>
       </c>
       <c r="O33">
-        <v>5.50538128</v>
+        <v>5.45028736</v>
       </c>
       <c r="P33">
-        <v>10.22427952</v>
+        <v>10.12196224</v>
       </c>
       <c r="Q33">
-        <v>13.12427952</v>
+        <v>13.02196224</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1969526558510239</v>
+        <v>0.1985733418446098</v>
       </c>
       <c r="T33">
-        <v>0.9244308269886126</v>
+        <v>0.9343427407747397</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.123101968668478</v>
+        <v>5.824490022524667</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1465322724543347</v>
+        <v>0.1460242623714629</v>
       </c>
       <c r="C34">
-        <v>149.7077925826549</v>
+        <v>148.8203718448172</v>
       </c>
       <c r="D34">
-        <v>184.7757925826549</v>
+        <v>185.7123718448172</v>
       </c>
       <c r="E34">
-        <v>58.368</v>
+        <v>60.19200000000001</v>
       </c>
       <c r="F34">
-        <v>58.368</v>
+        <v>60.19200000000001</v>
       </c>
       <c r="G34">
         <v>23.3</v>
@@ -4075,28 +4075,28 @@
         <v>18.8</v>
       </c>
       <c r="M34">
-        <v>3.2277504</v>
+        <v>3.328617600000001</v>
       </c>
       <c r="N34">
-        <v>15.5722496</v>
+        <v>15.4713824</v>
       </c>
       <c r="O34">
-        <v>5.45028736</v>
+        <v>5.41498384</v>
       </c>
       <c r="P34">
-        <v>10.12196224</v>
+        <v>10.05639856</v>
       </c>
       <c r="Q34">
-        <v>13.02196224</v>
+        <v>12.95639856</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1985733418446098</v>
+        <v>0.2002424065245715</v>
       </c>
       <c r="T34">
-        <v>0.9343427407747397</v>
+        <v>0.9445505325843333</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.824490022524667</v>
+        <v>5.647990324872402</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1460242623714629</v>
+        <v>0.145516252288591</v>
       </c>
       <c r="C35">
-        <v>148.8203718448172</v>
+        <v>147.9424940189455</v>
       </c>
       <c r="D35">
-        <v>185.7123718448172</v>
+        <v>186.6584940189455</v>
       </c>
       <c r="E35">
-        <v>60.19200000000001</v>
+        <v>62.01600000000001</v>
       </c>
       <c r="F35">
-        <v>60.19200000000001</v>
+        <v>62.01600000000001</v>
       </c>
       <c r="G35">
         <v>23.3</v>
@@ -4157,28 +4157,28 @@
         <v>18.8</v>
       </c>
       <c r="M35">
-        <v>3.328617600000001</v>
+        <v>3.4294848</v>
       </c>
       <c r="N35">
-        <v>15.4713824</v>
+        <v>15.3705152</v>
       </c>
       <c r="O35">
-        <v>5.41498384</v>
+        <v>5.379680319999999</v>
       </c>
       <c r="P35">
-        <v>10.05639856</v>
+        <v>9.990834880000001</v>
       </c>
       <c r="Q35">
-        <v>12.95639856</v>
+        <v>12.89083488</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2002424065245715</v>
+        <v>0.2019620489221077</v>
       </c>
       <c r="T35">
-        <v>0.9445505325843333</v>
+        <v>0.9550676514184601</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.647990324872402</v>
+        <v>5.481872962376156</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.145516252288591</v>
+        <v>0.1450082422057192</v>
       </c>
       <c r="C36">
-        <v>147.9424940189455</v>
+        <v>147.0743057026024</v>
       </c>
       <c r="D36">
-        <v>186.6584940189455</v>
+        <v>187.6143057026024</v>
       </c>
       <c r="E36">
-        <v>62.01600000000001</v>
+        <v>63.84000000000001</v>
       </c>
       <c r="F36">
-        <v>62.01600000000001</v>
+        <v>63.84000000000001</v>
       </c>
       <c r="G36">
         <v>23.3</v>
@@ -4239,28 +4239,28 @@
         <v>18.8</v>
       </c>
       <c r="M36">
-        <v>3.4294848</v>
+        <v>3.530352000000001</v>
       </c>
       <c r="N36">
-        <v>15.3705152</v>
+        <v>15.269648</v>
       </c>
       <c r="O36">
-        <v>5.379680319999999</v>
+        <v>5.3443768</v>
       </c>
       <c r="P36">
-        <v>9.990834880000001</v>
+        <v>9.925271200000001</v>
       </c>
       <c r="Q36">
-        <v>12.89083488</v>
+        <v>12.8252712</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2019620489221077</v>
+        <v>0.2037346033934142</v>
       </c>
       <c r="T36">
-        <v>0.9550676514184601</v>
+        <v>0.9659083739090215</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.481872962376156</v>
+        <v>5.32524802059398</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1450082422057192</v>
+        <v>0.1445002321228474</v>
       </c>
       <c r="C37">
-        <v>147.0743057026024</v>
+        <v>146.2159565115011</v>
       </c>
       <c r="D37">
-        <v>187.6143057026024</v>
+        <v>188.5799565115011</v>
       </c>
       <c r="E37">
-        <v>63.84000000000001</v>
+        <v>65.66400000000002</v>
       </c>
       <c r="F37">
-        <v>63.84000000000001</v>
+        <v>65.66400000000002</v>
       </c>
       <c r="G37">
         <v>23.3</v>
@@ -4321,28 +4321,28 @@
         <v>18.8</v>
       </c>
       <c r="M37">
-        <v>3.530352000000001</v>
+        <v>3.631219200000001</v>
       </c>
       <c r="N37">
-        <v>15.269648</v>
+        <v>15.1687808</v>
       </c>
       <c r="O37">
-        <v>5.3443768</v>
+        <v>5.30907328</v>
       </c>
       <c r="P37">
-        <v>9.925271200000001</v>
+        <v>9.859707520000001</v>
       </c>
       <c r="Q37">
-        <v>12.8252712</v>
+        <v>12.75970752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2037346033934142</v>
+        <v>0.2055625501919491</v>
       </c>
       <c r="T37">
-        <v>0.9659083739090215</v>
+        <v>0.977087868977413</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.32524802059398</v>
+        <v>5.177324464466369</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1445002321228474</v>
+        <v>0.1439922220399756</v>
       </c>
       <c r="C38">
-        <v>146.2159565115011</v>
+        <v>145.3675991575792</v>
       </c>
       <c r="D38">
-        <v>188.5799565115011</v>
+        <v>189.5555991575792</v>
       </c>
       <c r="E38">
-        <v>65.664</v>
+        <v>67.488</v>
       </c>
       <c r="F38">
-        <v>65.664</v>
+        <v>67.488</v>
       </c>
       <c r="G38">
         <v>23.3</v>
@@ -4403,28 +4403,28 @@
         <v>18.8</v>
       </c>
       <c r="M38">
-        <v>3.6312192</v>
+        <v>3.7320864</v>
       </c>
       <c r="N38">
-        <v>15.1687808</v>
+        <v>15.0679136</v>
       </c>
       <c r="O38">
-        <v>5.30907328</v>
+        <v>5.27376976</v>
       </c>
       <c r="P38">
-        <v>9.859707520000001</v>
+        <v>9.79414384</v>
       </c>
       <c r="Q38">
-        <v>12.75970752</v>
+        <v>12.69414384</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2055625501919491</v>
+        <v>0.2074485270475804</v>
       </c>
       <c r="T38">
-        <v>0.977087868977413</v>
+        <v>0.9886222686511501</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.17732446446637</v>
+        <v>5.037396776237549</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1439922220399756</v>
+        <v>0.1434842119571038</v>
       </c>
       <c r="C39">
-        <v>145.3675991575792</v>
+        <v>144.529389529509</v>
       </c>
       <c r="D39">
-        <v>189.5555991575792</v>
+        <v>190.541389529509</v>
       </c>
       <c r="E39">
-        <v>67.488</v>
+        <v>69.312</v>
       </c>
       <c r="F39">
-        <v>67.488</v>
+        <v>69.312</v>
       </c>
       <c r="G39">
         <v>23.3</v>
@@ -4485,28 +4485,28 @@
         <v>18.8</v>
       </c>
       <c r="M39">
-        <v>3.7320864</v>
+        <v>3.8329536</v>
       </c>
       <c r="N39">
-        <v>15.0679136</v>
+        <v>14.9670464</v>
       </c>
       <c r="O39">
-        <v>5.27376976</v>
+        <v>5.23846624</v>
       </c>
       <c r="P39">
-        <v>9.79414384</v>
+        <v>9.72858016</v>
       </c>
       <c r="Q39">
-        <v>12.69414384</v>
+        <v>12.62858016</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2074485270475804</v>
+        <v>0.2093953418662964</v>
       </c>
       <c r="T39">
-        <v>0.9886222686511501</v>
+        <v>1.000528745733718</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.037396776237549</v>
+        <v>4.904833703178666</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1434842119571038</v>
+        <v>0.142976201874232</v>
       </c>
       <c r="C40">
-        <v>144.529389529509</v>
+        <v>143.7014867757326</v>
       </c>
       <c r="D40">
-        <v>190.541389529509</v>
+        <v>191.5374867757326</v>
       </c>
       <c r="E40">
-        <v>69.312</v>
+        <v>71.13600000000001</v>
       </c>
       <c r="F40">
-        <v>69.312</v>
+        <v>71.13600000000001</v>
       </c>
       <c r="G40">
         <v>23.3</v>
@@ -4567,28 +4567,28 @@
         <v>18.8</v>
       </c>
       <c r="M40">
-        <v>3.8329536</v>
+        <v>3.933820800000001</v>
       </c>
       <c r="N40">
-        <v>14.9670464</v>
+        <v>14.8661792</v>
       </c>
       <c r="O40">
-        <v>5.23846624</v>
+        <v>5.20316272</v>
       </c>
       <c r="P40">
-        <v>9.72858016</v>
+        <v>9.66301648</v>
       </c>
       <c r="Q40">
-        <v>12.62858016</v>
+        <v>12.56301648</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2093953418662964</v>
+        <v>0.2114059866790688</v>
       </c>
       <c r="T40">
-        <v>1.000528745733718</v>
+        <v>1.012825599114074</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.904833703178666</v>
+        <v>4.779068736430494</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.142976201874232</v>
+        <v>0.1424681917913602</v>
       </c>
       <c r="C41">
-        <v>143.7014867757326</v>
+        <v>142.8840533901161</v>
       </c>
       <c r="D41">
-        <v>191.5374867757326</v>
+        <v>192.5440533901161</v>
       </c>
       <c r="E41">
-        <v>71.13600000000001</v>
+        <v>72.96000000000001</v>
       </c>
       <c r="F41">
-        <v>71.13600000000001</v>
+        <v>72.96000000000001</v>
       </c>
       <c r="G41">
         <v>23.3</v>
@@ -4649,28 +4649,28 @@
         <v>18.8</v>
       </c>
       <c r="M41">
-        <v>3.933820800000001</v>
+        <v>4.034688000000001</v>
       </c>
       <c r="N41">
-        <v>14.8661792</v>
+        <v>14.765312</v>
       </c>
       <c r="O41">
-        <v>5.20316272</v>
+        <v>5.1678592</v>
       </c>
       <c r="P41">
-        <v>9.66301648</v>
+        <v>9.597452799999999</v>
       </c>
       <c r="Q41">
-        <v>12.56301648</v>
+        <v>12.4974528</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2114059866790688</v>
+        <v>0.2134836529856003</v>
       </c>
       <c r="T41">
-        <v>1.012825599114074</v>
+        <v>1.025532347607109</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.779068736430494</v>
+        <v>4.659592018019731</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1424681917913602</v>
+        <v>0.1419601817084884</v>
       </c>
       <c r="C42">
-        <v>142.8840533901161</v>
+        <v>142.0772553003174</v>
       </c>
       <c r="D42">
-        <v>192.5440533901161</v>
+        <v>193.5612553003174</v>
       </c>
       <c r="E42">
-        <v>72.96000000000001</v>
+        <v>74.78400000000001</v>
       </c>
       <c r="F42">
-        <v>72.96000000000001</v>
+        <v>74.78400000000001</v>
       </c>
       <c r="G42">
         <v>23.3</v>
@@ -4731,28 +4731,28 @@
         <v>18.8</v>
       </c>
       <c r="M42">
-        <v>4.034688000000001</v>
+        <v>4.135555200000001</v>
       </c>
       <c r="N42">
-        <v>14.765312</v>
+        <v>14.6644448</v>
       </c>
       <c r="O42">
-        <v>5.1678592</v>
+        <v>5.132555679999999</v>
       </c>
       <c r="P42">
-        <v>9.597452799999999</v>
+        <v>9.531889120000001</v>
       </c>
       <c r="Q42">
-        <v>12.4974528</v>
+        <v>12.43188912</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2134836529856003</v>
+        <v>0.2156317486584549</v>
       </c>
       <c r="T42">
-        <v>1.025532347607109</v>
+        <v>1.038669833337196</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.659592018019731</v>
+        <v>4.545943432214373</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1419601817084884</v>
+        <v>0.1421346716256165</v>
       </c>
       <c r="C43">
-        <v>142.0772553003174</v>
+        <v>139.9026599557064</v>
       </c>
       <c r="D43">
-        <v>193.5612553003174</v>
+        <v>193.2106599557064</v>
       </c>
       <c r="E43">
-        <v>74.78400000000001</v>
+        <v>76.608</v>
       </c>
       <c r="F43">
-        <v>74.78400000000001</v>
+        <v>76.608</v>
       </c>
       <c r="G43">
         <v>23.3</v>
@@ -4813,45 +4813,45 @@
         <v>18.8</v>
       </c>
       <c r="M43">
-        <v>4.135555200000001</v>
+        <v>4.427942400000001</v>
       </c>
       <c r="N43">
-        <v>14.6644448</v>
+        <v>14.3720576</v>
       </c>
       <c r="O43">
-        <v>5.132555679999999</v>
+        <v>5.03022016</v>
       </c>
       <c r="P43">
-        <v>9.531889120000001</v>
+        <v>9.341837439999999</v>
       </c>
       <c r="Q43">
-        <v>12.43188912</v>
+        <v>12.24183744</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2156317486584549</v>
+        <v>0.2178539165958906</v>
       </c>
       <c r="T43">
-        <v>1.038669833337196</v>
+        <v>1.052260335816597</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.545943432214373</v>
+        <v>4.245764353212905</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1421346716256165</v>
+        <v>0.1416429115427447</v>
       </c>
       <c r="C44">
-        <v>139.9026599557064</v>
+        <v>139.0700039019841</v>
       </c>
       <c r="D44">
-        <v>193.2106599557063</v>
+        <v>194.2020039019841</v>
       </c>
       <c r="E44">
-        <v>76.608</v>
+        <v>78.432</v>
       </c>
       <c r="F44">
-        <v>76.608</v>
+        <v>78.432</v>
       </c>
       <c r="G44">
         <v>23.3</v>
@@ -4895,28 +4895,28 @@
         <v>18.8</v>
       </c>
       <c r="M44">
-        <v>4.427942400000001</v>
+        <v>4.5333696</v>
       </c>
       <c r="N44">
-        <v>14.3720576</v>
+        <v>14.2666304</v>
       </c>
       <c r="O44">
-        <v>5.03022016</v>
+        <v>4.993320639999999</v>
       </c>
       <c r="P44">
-        <v>9.341837439999999</v>
+        <v>9.27330976</v>
       </c>
       <c r="Q44">
-        <v>12.24183744</v>
+        <v>12.17330976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2178539165958906</v>
+        <v>0.2201540553381486</v>
       </c>
       <c r="T44">
-        <v>1.052260335816597</v>
+        <v>1.066327698032117</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.245764353212905</v>
+        <v>4.147025647324233</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1416429115427447</v>
+        <v>0.1411511514598729</v>
       </c>
       <c r="C45">
-        <v>139.0700039019841</v>
+        <v>138.2475732807546</v>
       </c>
       <c r="D45">
-        <v>194.2020039019841</v>
+        <v>195.2035732807545</v>
       </c>
       <c r="E45">
-        <v>78.432</v>
+        <v>80.256</v>
       </c>
       <c r="F45">
-        <v>78.432</v>
+        <v>80.256</v>
       </c>
       <c r="G45">
         <v>23.3</v>
@@ -4977,28 +4977,28 @@
         <v>18.8</v>
       </c>
       <c r="M45">
-        <v>4.5333696</v>
+        <v>4.638796800000001</v>
       </c>
       <c r="N45">
-        <v>14.2666304</v>
+        <v>14.1612032</v>
       </c>
       <c r="O45">
-        <v>4.993320639999999</v>
+        <v>4.956421119999999</v>
       </c>
       <c r="P45">
-        <v>9.27330976</v>
+        <v>9.204782080000001</v>
       </c>
       <c r="Q45">
-        <v>12.17330976</v>
+        <v>12.10478208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2201540553381486</v>
+        <v>0.2225363418926302</v>
       </c>
       <c r="T45">
-        <v>1.066327698032117</v>
+        <v>1.080897466041048</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.147025647324233</v>
+        <v>4.052775064430501</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1411511514598729</v>
+        <v>0.1416831413770011</v>
       </c>
       <c r="C46">
-        <v>138.2475732807546</v>
+        <v>135.3405222742753</v>
       </c>
       <c r="D46">
-        <v>195.2035732807545</v>
+        <v>194.1205222742753</v>
       </c>
       <c r="E46">
-        <v>80.256</v>
+        <v>82.08</v>
       </c>
       <c r="F46">
-        <v>80.256</v>
+        <v>82.08</v>
       </c>
       <c r="G46">
         <v>23.3</v>
@@ -5059,45 +5059,45 @@
         <v>18.8</v>
       </c>
       <c r="M46">
-        <v>4.638796800000001</v>
+        <v>5.031504</v>
       </c>
       <c r="N46">
-        <v>14.1612032</v>
+        <v>13.768496</v>
       </c>
       <c r="O46">
-        <v>4.956421119999999</v>
+        <v>4.8189736</v>
       </c>
       <c r="P46">
-        <v>9.204782080000001</v>
+        <v>8.949522400000001</v>
       </c>
       <c r="Q46">
-        <v>12.10478208</v>
+        <v>11.8495224</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2225363418926302</v>
+        <v>0.2250052570490929</v>
       </c>
       <c r="T46">
-        <v>1.080897466041048</v>
+        <v>1.095997043795758</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.35</v>
       </c>
       <c r="W46">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.052775064430501</v>
+        <v>3.736457329657295</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1416831413770011</v>
+        <v>0.1412141312941293</v>
       </c>
       <c r="C47">
-        <v>135.3405222742753</v>
+        <v>134.4707256087722</v>
       </c>
       <c r="D47">
-        <v>194.1205222742753</v>
+        <v>195.0747256087722</v>
       </c>
       <c r="E47">
-        <v>82.08</v>
+        <v>83.90400000000001</v>
       </c>
       <c r="F47">
-        <v>82.08</v>
+        <v>83.90400000000001</v>
       </c>
       <c r="G47">
         <v>23.3</v>
@@ -5141,28 +5141,28 @@
         <v>18.8</v>
       </c>
       <c r="M47">
-        <v>5.031504</v>
+        <v>5.143315200000001</v>
       </c>
       <c r="N47">
-        <v>13.768496</v>
+        <v>13.6566848</v>
       </c>
       <c r="O47">
-        <v>4.8189736</v>
+        <v>4.77983968</v>
       </c>
       <c r="P47">
-        <v>8.949522400000001</v>
+        <v>8.87684512</v>
       </c>
       <c r="Q47">
-        <v>11.8495224</v>
+        <v>11.77684512</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2250052570490929</v>
+        <v>0.2275656135076468</v>
       </c>
       <c r="T47">
-        <v>1.095997043795758</v>
+        <v>1.111655865171014</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.736457329657295</v>
+        <v>3.655229996403876</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1412141312941293</v>
+        <v>0.1407451212112575</v>
       </c>
       <c r="C48">
-        <v>134.4707256087722</v>
+        <v>133.610356094012</v>
       </c>
       <c r="D48">
-        <v>195.0747256087722</v>
+        <v>196.038356094012</v>
       </c>
       <c r="E48">
-        <v>83.90400000000001</v>
+        <v>85.72800000000001</v>
       </c>
       <c r="F48">
-        <v>83.90400000000001</v>
+        <v>85.72800000000001</v>
       </c>
       <c r="G48">
         <v>23.3</v>
@@ -5223,28 +5223,28 @@
         <v>18.8</v>
       </c>
       <c r="M48">
-        <v>5.143315200000001</v>
+        <v>5.255126400000001</v>
       </c>
       <c r="N48">
-        <v>13.6566848</v>
+        <v>13.5448736</v>
       </c>
       <c r="O48">
-        <v>4.77983968</v>
+        <v>4.740705759999999</v>
       </c>
       <c r="P48">
-        <v>8.87684512</v>
+        <v>8.80416784</v>
       </c>
       <c r="Q48">
-        <v>11.77684512</v>
+        <v>11.70416784</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2275656135076468</v>
+        <v>0.2302225871910518</v>
       </c>
       <c r="T48">
-        <v>1.111655865171014</v>
+        <v>1.12790558546609</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.655229996403876</v>
+        <v>3.577459145416559</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1407451212112575</v>
+        <v>0.1402761111283856</v>
       </c>
       <c r="C49">
-        <v>133.610356094012</v>
+        <v>132.7595541283042</v>
       </c>
       <c r="D49">
-        <v>196.038356094012</v>
+        <v>197.0115541283042</v>
       </c>
       <c r="E49">
-        <v>85.72800000000001</v>
+        <v>87.55200000000001</v>
       </c>
       <c r="F49">
-        <v>85.72800000000001</v>
+        <v>87.55200000000001</v>
       </c>
       <c r="G49">
         <v>23.3</v>
@@ -5305,28 +5305,28 @@
         <v>18.8</v>
       </c>
       <c r="M49">
-        <v>5.255126400000001</v>
+        <v>5.366937600000001</v>
       </c>
       <c r="N49">
-        <v>13.5448736</v>
+        <v>13.4330624</v>
       </c>
       <c r="O49">
-        <v>4.740705759999999</v>
+        <v>4.70157184</v>
       </c>
       <c r="P49">
-        <v>8.80416784</v>
+        <v>8.731490560000001</v>
       </c>
       <c r="Q49">
-        <v>11.70416784</v>
+        <v>11.63149056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2302225871910518</v>
+        <v>0.2329817521699724</v>
       </c>
       <c r="T49">
-        <v>1.12790558546609</v>
+        <v>1.144780295003285</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.577459145416559</v>
+        <v>3.502928746553714</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1402761111283856</v>
+        <v>0.1406989010455139</v>
       </c>
       <c r="C50">
-        <v>132.7595541283042</v>
+        <v>130.0578358647043</v>
       </c>
       <c r="D50">
-        <v>197.0115541283042</v>
+        <v>196.1338358647043</v>
       </c>
       <c r="E50">
-        <v>87.55199999999999</v>
+        <v>89.376</v>
       </c>
       <c r="F50">
-        <v>87.55199999999999</v>
+        <v>89.376</v>
       </c>
       <c r="G50">
         <v>23.3</v>
@@ -5387,45 +5387,45 @@
         <v>18.8</v>
       </c>
       <c r="M50">
-        <v>5.3669376</v>
+        <v>5.729001600000001</v>
       </c>
       <c r="N50">
-        <v>13.4330624</v>
+        <v>13.0709984</v>
       </c>
       <c r="O50">
-        <v>4.70157184</v>
+        <v>4.574849439999999</v>
       </c>
       <c r="P50">
-        <v>8.731490560000001</v>
+        <v>8.496148960000001</v>
       </c>
       <c r="Q50">
-        <v>11.63149056</v>
+        <v>11.39614896</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2329817521699724</v>
+        <v>0.235849119697086</v>
       </c>
       <c r="T50">
-        <v>1.144780295003285</v>
+        <v>1.162316757855663</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.502928746553715</v>
+        <v>3.281549092253701</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1406989010455139</v>
+        <v>0.140248090962642</v>
       </c>
       <c r="C51">
-        <v>130.0578358647043</v>
+        <v>129.1700020687953</v>
       </c>
       <c r="D51">
-        <v>196.1338358647043</v>
+        <v>197.0700020687953</v>
       </c>
       <c r="E51">
-        <v>89.376</v>
+        <v>91.2</v>
       </c>
       <c r="F51">
-        <v>89.376</v>
+        <v>91.2</v>
       </c>
       <c r="G51">
         <v>23.3</v>
@@ -5469,28 +5469,28 @@
         <v>18.8</v>
       </c>
       <c r="M51">
-        <v>5.729001600000001</v>
+        <v>5.84592</v>
       </c>
       <c r="N51">
-        <v>13.0709984</v>
+        <v>12.95408</v>
       </c>
       <c r="O51">
-        <v>4.574849439999999</v>
+        <v>4.533928</v>
       </c>
       <c r="P51">
-        <v>8.496148960000001</v>
+        <v>8.420152000000002</v>
       </c>
       <c r="Q51">
-        <v>11.39614896</v>
+        <v>11.320152</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.235849119697086</v>
+        <v>0.238831181925284</v>
       </c>
       <c r="T51">
-        <v>1.162316757855663</v>
+        <v>1.180554679222137</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.281549092253701</v>
+        <v>3.215918110408627</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.140248090962642</v>
+        <v>0.1397972808797702</v>
       </c>
       <c r="C52">
-        <v>129.1700020687953</v>
+        <v>128.2911479616624</v>
       </c>
       <c r="D52">
-        <v>197.0700020687953</v>
+        <v>198.0151479616624</v>
       </c>
       <c r="E52">
-        <v>91.2</v>
+        <v>93.024</v>
       </c>
       <c r="F52">
-        <v>91.2</v>
+        <v>93.024</v>
       </c>
       <c r="G52">
         <v>23.3</v>
@@ -5551,28 +5551,28 @@
         <v>18.8</v>
       </c>
       <c r="M52">
-        <v>5.84592</v>
+        <v>5.962838400000001</v>
       </c>
       <c r="N52">
-        <v>12.95408</v>
+        <v>12.8371616</v>
       </c>
       <c r="O52">
-        <v>4.533928</v>
+        <v>4.49300656</v>
       </c>
       <c r="P52">
-        <v>8.420152000000002</v>
+        <v>8.34415504</v>
       </c>
       <c r="Q52">
-        <v>11.320152</v>
+        <v>11.24415504</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.238831181925284</v>
+        <v>0.2419349609791229</v>
       </c>
       <c r="T52">
-        <v>1.180554679222137</v>
+        <v>1.199537005542345</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.215918110408627</v>
+        <v>3.152860892557477</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1397972808797702</v>
+        <v>0.1393464707968984</v>
       </c>
       <c r="C53">
-        <v>128.2911479616624</v>
+        <v>127.4214033654421</v>
       </c>
       <c r="D53">
-        <v>198.0151479616624</v>
+        <v>198.9694033654421</v>
       </c>
       <c r="E53">
-        <v>93.024</v>
+        <v>94.84800000000001</v>
       </c>
       <c r="F53">
-        <v>93.024</v>
+        <v>94.84800000000001</v>
       </c>
       <c r="G53">
         <v>23.3</v>
@@ -5633,28 +5633,28 @@
         <v>18.8</v>
       </c>
       <c r="M53">
-        <v>5.962838400000001</v>
+        <v>6.079756800000001</v>
       </c>
       <c r="N53">
-        <v>12.8371616</v>
+        <v>12.7202432</v>
       </c>
       <c r="O53">
-        <v>4.49300656</v>
+        <v>4.45208512</v>
       </c>
       <c r="P53">
-        <v>8.34415504</v>
+        <v>8.268158079999999</v>
       </c>
       <c r="Q53">
-        <v>11.24415504</v>
+        <v>11.16815808</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2419349609791229</v>
+        <v>0.245168064160205</v>
       </c>
       <c r="T53">
-        <v>1.199537005542345</v>
+        <v>1.219310262125894</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.152860892557477</v>
+        <v>3.092228952315987</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1393464707968984</v>
+        <v>0.1388956607140266</v>
       </c>
       <c r="C54">
-        <v>127.4214033654421</v>
+        <v>126.5609006168948</v>
       </c>
       <c r="D54">
-        <v>198.9694033654421</v>
+        <v>199.9329006168948</v>
       </c>
       <c r="E54">
-        <v>94.84800000000001</v>
+        <v>96.67200000000001</v>
       </c>
       <c r="F54">
-        <v>94.84800000000001</v>
+        <v>96.67200000000001</v>
       </c>
       <c r="G54">
         <v>23.3</v>
@@ -5715,28 +5715,28 @@
         <v>18.8</v>
       </c>
       <c r="M54">
-        <v>6.079756800000001</v>
+        <v>6.196675200000001</v>
       </c>
       <c r="N54">
-        <v>12.7202432</v>
+        <v>12.6033248</v>
       </c>
       <c r="O54">
-        <v>4.45208512</v>
+        <v>4.41116368</v>
       </c>
       <c r="P54">
-        <v>8.268158079999999</v>
+        <v>8.19216112</v>
       </c>
       <c r="Q54">
-        <v>11.16815808</v>
+        <v>11.09216112</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.245168064160205</v>
+        <v>0.2485387462000566</v>
       </c>
       <c r="T54">
-        <v>1.219310262125894</v>
+        <v>1.239924933883212</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.092228952315987</v>
+        <v>3.033885009819459</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1388956607140266</v>
+        <v>0.1411826506311548</v>
       </c>
       <c r="C55">
-        <v>126.5609006168948</v>
+        <v>119.9431092430191</v>
       </c>
       <c r="D55">
-        <v>199.9329006168948</v>
+        <v>195.1391092430191</v>
       </c>
       <c r="E55">
-        <v>96.67200000000001</v>
+        <v>98.49600000000001</v>
       </c>
       <c r="F55">
-        <v>96.67200000000001</v>
+        <v>98.49600000000001</v>
       </c>
       <c r="G55">
         <v>23.3</v>
@@ -5797,45 +5797,45 @@
         <v>18.8</v>
       </c>
       <c r="M55">
-        <v>6.196675200000001</v>
+        <v>7.081862400000001</v>
       </c>
       <c r="N55">
-        <v>12.6033248</v>
+        <v>11.7181376</v>
       </c>
       <c r="O55">
-        <v>4.41116368</v>
+        <v>4.10134816</v>
       </c>
       <c r="P55">
-        <v>8.19216112</v>
+        <v>7.616789439999999</v>
       </c>
       <c r="Q55">
-        <v>11.09216112</v>
+        <v>10.51678944</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2485387462000566</v>
+        <v>0.2520559796329451</v>
       </c>
       <c r="T55">
-        <v>1.239924933883212</v>
+        <v>1.261435895716935</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.35</v>
       </c>
       <c r="W55">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.033885009819459</v>
+        <v>2.654668918729627</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1411826506311548</v>
+        <v>0.140782540548283</v>
       </c>
       <c r="C56">
-        <v>119.9431092430191</v>
+        <v>118.9411247915616</v>
       </c>
       <c r="D56">
-        <v>195.1391092430191</v>
+        <v>195.9611247915616</v>
       </c>
       <c r="E56">
-        <v>98.49600000000001</v>
+        <v>100.32</v>
       </c>
       <c r="F56">
-        <v>98.49600000000001</v>
+        <v>100.32</v>
       </c>
       <c r="G56">
         <v>23.3</v>
@@ -5879,28 +5879,28 @@
         <v>18.8</v>
       </c>
       <c r="M56">
-        <v>7.081862400000001</v>
+        <v>7.213008000000001</v>
       </c>
       <c r="N56">
-        <v>11.7181376</v>
+        <v>11.586992</v>
       </c>
       <c r="O56">
-        <v>4.10134816</v>
+        <v>4.0554472</v>
       </c>
       <c r="P56">
-        <v>7.616789439999999</v>
+        <v>7.531544799999999</v>
       </c>
       <c r="Q56">
-        <v>10.51678944</v>
+        <v>10.4315448</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2520559796329451</v>
+        <v>0.2557295345517399</v>
       </c>
       <c r="T56">
-        <v>1.261435895716935</v>
+        <v>1.283902900298823</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.654668918729627</v>
+        <v>2.606402211116361</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.140782540548283</v>
+        <v>0.1403824304654111</v>
       </c>
       <c r="C57">
-        <v>118.9411247915616</v>
+        <v>117.9460950505642</v>
       </c>
       <c r="D57">
-        <v>195.9611247915616</v>
+        <v>196.7900950505642</v>
       </c>
       <c r="E57">
-        <v>100.32</v>
+        <v>102.144</v>
       </c>
       <c r="F57">
-        <v>100.32</v>
+        <v>102.144</v>
       </c>
       <c r="G57">
         <v>23.3</v>
@@ -5961,28 +5961,28 @@
         <v>18.8</v>
       </c>
       <c r="M57">
-        <v>7.213008000000001</v>
+        <v>7.344153600000002</v>
       </c>
       <c r="N57">
-        <v>11.586992</v>
+        <v>11.4558464</v>
       </c>
       <c r="O57">
-        <v>4.0554472</v>
+        <v>4.00954624</v>
       </c>
       <c r="P57">
-        <v>7.531544799999999</v>
+        <v>7.446300159999999</v>
       </c>
       <c r="Q57">
-        <v>10.4315448</v>
+        <v>10.34630016</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2557295345517399</v>
+        <v>0.2595700692395708</v>
       </c>
       <c r="T57">
-        <v>1.283902900298823</v>
+        <v>1.307391132361706</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.606402211116361</v>
+        <v>2.559859314489283</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1403824304654111</v>
+        <v>0.1399823203825393</v>
       </c>
       <c r="C58">
-        <v>117.9460950505642</v>
+        <v>116.9581086560819</v>
       </c>
       <c r="D58">
-        <v>196.7900950505642</v>
+        <v>197.626108656082</v>
       </c>
       <c r="E58">
-        <v>102.144</v>
+        <v>103.968</v>
       </c>
       <c r="F58">
-        <v>102.144</v>
+        <v>103.968</v>
       </c>
       <c r="G58">
         <v>23.3</v>
@@ -6043,28 +6043,28 @@
         <v>18.8</v>
       </c>
       <c r="M58">
-        <v>7.344153600000002</v>
+        <v>7.475299200000002</v>
       </c>
       <c r="N58">
-        <v>11.4558464</v>
+        <v>11.3247008</v>
       </c>
       <c r="O58">
-        <v>4.00954624</v>
+        <v>3.963645279999999</v>
       </c>
       <c r="P58">
-        <v>7.446300159999999</v>
+        <v>7.361055519999999</v>
       </c>
       <c r="Q58">
-        <v>10.34630016</v>
+        <v>10.26105552</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2595700692395708</v>
+        <v>0.2635892334477659</v>
       </c>
       <c r="T58">
-        <v>1.307391132361706</v>
+        <v>1.33197184033449</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.559859314489283</v>
+        <v>2.514949501954383</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1399823203825393</v>
+        <v>0.1410525102996675</v>
       </c>
       <c r="C59">
-        <v>116.9581086560819</v>
+        <v>112.9137213069229</v>
       </c>
       <c r="D59">
-        <v>197.626108656082</v>
+        <v>195.4057213069229</v>
       </c>
       <c r="E59">
-        <v>103.968</v>
+        <v>105.792</v>
       </c>
       <c r="F59">
-        <v>103.968</v>
+        <v>105.792</v>
       </c>
       <c r="G59">
         <v>23.3</v>
@@ -6125,45 +6125,45 @@
         <v>18.8</v>
       </c>
       <c r="M59">
-        <v>7.475299200000002</v>
+        <v>8.019033600000002</v>
       </c>
       <c r="N59">
-        <v>11.3247008</v>
+        <v>10.7809664</v>
       </c>
       <c r="O59">
-        <v>3.963645279999999</v>
+        <v>3.773338239999999</v>
       </c>
       <c r="P59">
-        <v>7.361055519999999</v>
+        <v>7.007628159999999</v>
       </c>
       <c r="Q59">
-        <v>10.26105552</v>
+        <v>9.907628159999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2635892334477659</v>
+        <v>0.2677997864277798</v>
       </c>
       <c r="T59">
-        <v>1.33197184033449</v>
+        <v>1.357723058210741</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.514949501954383</v>
+        <v>2.344422150818771</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1410525102996675</v>
+        <v>0.1406777502167957</v>
       </c>
       <c r="C60">
-        <v>112.9137213069229</v>
+        <v>111.8615594264323</v>
       </c>
       <c r="D60">
-        <v>195.4057213069229</v>
+        <v>196.1775594264323</v>
       </c>
       <c r="E60">
-        <v>105.792</v>
+        <v>107.616</v>
       </c>
       <c r="F60">
-        <v>105.792</v>
+        <v>107.616</v>
       </c>
       <c r="G60">
         <v>23.3</v>
@@ -6207,28 +6207,28 @@
         <v>18.8</v>
       </c>
       <c r="M60">
-        <v>8.0190336</v>
+        <v>8.1572928</v>
       </c>
       <c r="N60">
-        <v>10.7809664</v>
+        <v>10.6427072</v>
       </c>
       <c r="O60">
-        <v>3.77333824</v>
+        <v>3.72494752</v>
       </c>
       <c r="P60">
-        <v>7.007628160000001</v>
+        <v>6.917759680000001</v>
       </c>
       <c r="Q60">
-        <v>9.90762816</v>
+        <v>9.817759679999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2677997864277797</v>
+        <v>0.272215732236087</v>
       </c>
       <c r="T60">
-        <v>1.357723058210741</v>
+        <v>1.384730433056564</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.344422150818772</v>
+        <v>2.304686182160827</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1406777502167957</v>
+        <v>0.1403029901339239</v>
       </c>
       <c r="C61">
-        <v>111.8615594264323</v>
+        <v>110.8155191325119</v>
       </c>
       <c r="D61">
-        <v>196.1775594264323</v>
+        <v>196.9555191325119</v>
       </c>
       <c r="E61">
-        <v>107.616</v>
+        <v>109.44</v>
       </c>
       <c r="F61">
-        <v>107.616</v>
+        <v>109.44</v>
       </c>
       <c r="G61">
         <v>23.3</v>
@@ -6289,28 +6289,28 @@
         <v>18.8</v>
       </c>
       <c r="M61">
-        <v>8.1572928</v>
+        <v>8.295552000000001</v>
       </c>
       <c r="N61">
-        <v>10.6427072</v>
+        <v>10.504448</v>
       </c>
       <c r="O61">
-        <v>3.72494752</v>
+        <v>3.6765568</v>
       </c>
       <c r="P61">
-        <v>6.917759680000001</v>
+        <v>6.8278912</v>
       </c>
       <c r="Q61">
-        <v>9.817759679999998</v>
+        <v>9.727891199999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.272215732236087</v>
+        <v>0.2768524753348097</v>
       </c>
       <c r="T61">
-        <v>1.384730433056564</v>
+        <v>1.413088176644679</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.304686182160827</v>
+        <v>2.266274745791479</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1403029901339239</v>
+        <v>0.139928230051052</v>
       </c>
       <c r="C62">
-        <v>110.8155191325119</v>
+        <v>109.775673542216</v>
       </c>
       <c r="D62">
-        <v>196.9555191325119</v>
+        <v>197.739673542216</v>
       </c>
       <c r="E62">
-        <v>109.44</v>
+        <v>111.264</v>
       </c>
       <c r="F62">
-        <v>109.44</v>
+        <v>111.264</v>
       </c>
       <c r="G62">
         <v>23.3</v>
@@ -6371,28 +6371,28 @@
         <v>18.8</v>
       </c>
       <c r="M62">
-        <v>8.295552000000001</v>
+        <v>8.433811200000001</v>
       </c>
       <c r="N62">
-        <v>10.504448</v>
+        <v>10.3661888</v>
       </c>
       <c r="O62">
-        <v>3.6765568</v>
+        <v>3.62816608</v>
       </c>
       <c r="P62">
-        <v>6.8278912</v>
+        <v>6.73802272</v>
       </c>
       <c r="Q62">
-        <v>9.727891199999998</v>
+        <v>9.638022719999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2768524753348097</v>
+        <v>0.2817270001309027</v>
       </c>
       <c r="T62">
-        <v>1.413088176644679</v>
+        <v>1.442900163493723</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.266274745791479</v>
+        <v>2.229122700778504</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.139928230051052</v>
+        <v>0.1395534699681803</v>
       </c>
       <c r="C63">
-        <v>109.775673542216</v>
+        <v>108.7420969416791</v>
       </c>
       <c r="D63">
-        <v>197.739673542216</v>
+        <v>198.5300969416791</v>
       </c>
       <c r="E63">
-        <v>111.264</v>
+        <v>113.088</v>
       </c>
       <c r="F63">
-        <v>111.264</v>
+        <v>113.088</v>
       </c>
       <c r="G63">
         <v>23.3</v>
@@ -6453,28 +6453,28 @@
         <v>18.8</v>
       </c>
       <c r="M63">
-        <v>8.433811200000001</v>
+        <v>8.572070400000001</v>
       </c>
       <c r="N63">
-        <v>10.3661888</v>
+        <v>10.2279296</v>
       </c>
       <c r="O63">
-        <v>3.62816608</v>
+        <v>3.57977536</v>
       </c>
       <c r="P63">
-        <v>6.73802272</v>
+        <v>6.64815424</v>
       </c>
       <c r="Q63">
-        <v>9.638022719999999</v>
+        <v>9.548154239999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2817270001309027</v>
+        <v>0.2868580788636322</v>
       </c>
       <c r="T63">
-        <v>1.442900163493723</v>
+        <v>1.474281202282191</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.229122700778504</v>
+        <v>2.193169108830464</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1395534699681803</v>
+        <v>0.1391787098853084</v>
       </c>
       <c r="C64">
-        <v>108.7420969416791</v>
+        <v>107.7148648095775</v>
       </c>
       <c r="D64">
-        <v>198.5300969416791</v>
+        <v>199.3268648095775</v>
       </c>
       <c r="E64">
-        <v>113.088</v>
+        <v>114.912</v>
       </c>
       <c r="F64">
-        <v>113.088</v>
+        <v>114.912</v>
       </c>
       <c r="G64">
         <v>23.3</v>
@@ -6535,28 +6535,28 @@
         <v>18.8</v>
       </c>
       <c r="M64">
-        <v>8.572070400000001</v>
+        <v>8.710329600000001</v>
       </c>
       <c r="N64">
-        <v>10.2279296</v>
+        <v>10.0896704</v>
       </c>
       <c r="O64">
-        <v>3.57977536</v>
+        <v>3.531384639999999</v>
       </c>
       <c r="P64">
-        <v>6.64815424</v>
+        <v>6.55828576</v>
       </c>
       <c r="Q64">
-        <v>9.548154239999999</v>
+        <v>9.458285759999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2868580788636322</v>
+        <v>0.2922665132035362</v>
       </c>
       <c r="T64">
-        <v>1.474281202282191</v>
+        <v>1.507358513437602</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.193169108830464</v>
+        <v>2.15835690075379</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1391787098853084</v>
+        <v>0.1388039498024366</v>
       </c>
       <c r="C65">
-        <v>107.7148648095775</v>
+        <v>106.6940538411541</v>
       </c>
       <c r="D65">
-        <v>199.3268648095775</v>
+        <v>200.1300538411541</v>
       </c>
       <c r="E65">
-        <v>114.912</v>
+        <v>116.736</v>
       </c>
       <c r="F65">
-        <v>114.912</v>
+        <v>116.736</v>
       </c>
       <c r="G65">
         <v>23.3</v>
@@ -6617,28 +6617,28 @@
         <v>18.8</v>
       </c>
       <c r="M65">
-        <v>8.710329600000001</v>
+        <v>8.848588800000002</v>
       </c>
       <c r="N65">
-        <v>10.0896704</v>
+        <v>9.951411199999999</v>
       </c>
       <c r="O65">
-        <v>3.531384639999999</v>
+        <v>3.482993919999999</v>
       </c>
       <c r="P65">
-        <v>6.55828576</v>
+        <v>6.46841728</v>
       </c>
       <c r="Q65">
-        <v>9.458285759999999</v>
+        <v>9.368417279999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2922665132035362</v>
+        <v>0.2979754161178795</v>
       </c>
       <c r="T65">
-        <v>1.507358513437602</v>
+        <v>1.542273452990536</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.15835690075379</v>
+        <v>2.124632574179512</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1388039498024366</v>
+        <v>0.1384291897195648</v>
       </c>
       <c r="C66">
-        <v>106.6940538411541</v>
+        <v>105.6797419728296</v>
       </c>
       <c r="D66">
-        <v>200.1300538411541</v>
+        <v>200.9397419728296</v>
       </c>
       <c r="E66">
-        <v>116.736</v>
+        <v>118.56</v>
       </c>
       <c r="F66">
-        <v>116.736</v>
+        <v>118.56</v>
       </c>
       <c r="G66">
         <v>23.3</v>
@@ -6699,28 +6699,28 @@
         <v>18.8</v>
       </c>
       <c r="M66">
-        <v>8.848588800000002</v>
+        <v>8.986848</v>
       </c>
       <c r="N66">
-        <v>9.951411199999999</v>
+        <v>9.813152000000001</v>
       </c>
       <c r="O66">
-        <v>3.482993919999999</v>
+        <v>3.4346032</v>
       </c>
       <c r="P66">
-        <v>6.46841728</v>
+        <v>6.378548800000001</v>
       </c>
       <c r="Q66">
-        <v>9.368417279999999</v>
+        <v>9.278548799999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2979754161178795</v>
+        <v>0.3040105420558994</v>
       </c>
       <c r="T66">
-        <v>1.542273452990536</v>
+        <v>1.579183531946496</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.124632574179512</v>
+        <v>2.091945919192135</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1384291897195648</v>
+        <v>0.138054429636693</v>
       </c>
       <c r="C67">
-        <v>105.6797419728296</v>
+        <v>104.672008407412</v>
       </c>
       <c r="D67">
-        <v>200.9397419728296</v>
+        <v>201.756008407412</v>
       </c>
       <c r="E67">
-        <v>118.56</v>
+        <v>120.384</v>
       </c>
       <c r="F67">
-        <v>118.56</v>
+        <v>120.384</v>
       </c>
       <c r="G67">
         <v>23.3</v>
@@ -6781,28 +6781,28 @@
         <v>18.8</v>
       </c>
       <c r="M67">
-        <v>8.986848</v>
+        <v>9.125107200000002</v>
       </c>
       <c r="N67">
-        <v>9.813152000000001</v>
+        <v>9.674892799999999</v>
       </c>
       <c r="O67">
-        <v>3.4346032</v>
+        <v>3.386212479999999</v>
       </c>
       <c r="P67">
-        <v>6.378548800000001</v>
+        <v>6.288680319999999</v>
       </c>
       <c r="Q67">
-        <v>9.278548799999999</v>
+        <v>9.188680319999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3040105420558994</v>
+        <v>0.3104006754020382</v>
       </c>
       <c r="T67">
-        <v>1.579183531946496</v>
+        <v>1.618264792017511</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.091945919192135</v>
+        <v>2.060249768901345</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.138054429636693</v>
+        <v>0.1376796695538212</v>
       </c>
       <c r="C68">
-        <v>104.672008407412</v>
+        <v>103.6709336399234</v>
       </c>
       <c r="D68">
-        <v>201.756008407412</v>
+        <v>202.5789336399234</v>
       </c>
       <c r="E68">
-        <v>120.384</v>
+        <v>122.208</v>
       </c>
       <c r="F68">
-        <v>120.384</v>
+        <v>122.208</v>
       </c>
       <c r="G68">
         <v>23.3</v>
@@ -6863,28 +6863,28 @@
         <v>18.8</v>
       </c>
       <c r="M68">
-        <v>9.125107200000002</v>
+        <v>9.263366400000002</v>
       </c>
       <c r="N68">
-        <v>9.674892799999999</v>
+        <v>9.536633599999998</v>
       </c>
       <c r="O68">
-        <v>3.386212479999999</v>
+        <v>3.337821759999999</v>
       </c>
       <c r="P68">
-        <v>6.288680319999999</v>
+        <v>6.198811839999999</v>
       </c>
       <c r="Q68">
-        <v>9.188680319999998</v>
+        <v>9.098811839999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3104006754020382</v>
+        <v>0.3171780895570339</v>
       </c>
       <c r="T68">
-        <v>1.618264792017511</v>
+        <v>1.659714613304952</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.060249768901345</v>
+        <v>2.029499772350579</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1376796695538212</v>
+        <v>0.1435813094709494</v>
       </c>
       <c r="C69">
-        <v>103.6709336399234</v>
+        <v>89.62018061721176</v>
       </c>
       <c r="D69">
-        <v>202.5789336399234</v>
+        <v>190.3521806172118</v>
       </c>
       <c r="E69">
-        <v>122.208</v>
+        <v>124.032</v>
       </c>
       <c r="F69">
-        <v>122.208</v>
+        <v>124.032</v>
       </c>
       <c r="G69">
         <v>23.3</v>
@@ -6945,45 +6945,45 @@
         <v>18.8</v>
       </c>
       <c r="M69">
-        <v>9.263366400000002</v>
+        <v>11.16288</v>
       </c>
       <c r="N69">
-        <v>9.536633599999998</v>
+        <v>7.637119999999999</v>
       </c>
       <c r="O69">
-        <v>3.337821759999999</v>
+        <v>2.672992</v>
       </c>
       <c r="P69">
-        <v>6.198811839999999</v>
+        <v>4.964128</v>
       </c>
       <c r="Q69">
-        <v>9.098811839999998</v>
+        <v>7.864127999999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3171780895570339</v>
+        <v>0.3243790920967168</v>
       </c>
       <c r="T69">
-        <v>1.659714613304952</v>
+        <v>1.703755048422858</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.029499772350579</v>
+        <v>1.684153193441119</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1435813094709494</v>
+        <v>0.1432988493880775</v>
       </c>
       <c r="C70">
-        <v>89.62018061721176</v>
+        <v>88.34764243496063</v>
       </c>
       <c r="D70">
-        <v>190.3521806172118</v>
+        <v>190.9036424349606</v>
       </c>
       <c r="E70">
-        <v>124.032</v>
+        <v>125.856</v>
       </c>
       <c r="F70">
-        <v>124.032</v>
+        <v>125.856</v>
       </c>
       <c r="G70">
         <v>23.3</v>
@@ -7027,28 +7027,28 @@
         <v>18.8</v>
       </c>
       <c r="M70">
-        <v>11.16288</v>
+        <v>11.32704</v>
       </c>
       <c r="N70">
-        <v>7.637119999999999</v>
+        <v>7.47296</v>
       </c>
       <c r="O70">
-        <v>2.672992</v>
+        <v>2.615536</v>
       </c>
       <c r="P70">
-        <v>4.964128</v>
+        <v>4.857424</v>
       </c>
       <c r="Q70">
-        <v>7.864127999999998</v>
+        <v>7.757423999999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3243790920967168</v>
+        <v>0.3320446754454114</v>
       </c>
       <c r="T70">
-        <v>1.703755048422858</v>
+        <v>1.750636801935467</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.684153193441119</v>
+        <v>1.659745176144871</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1432988493880775</v>
+        <v>0.1430163893052057</v>
       </c>
       <c r="C71">
-        <v>88.34764243496063</v>
+        <v>87.07830877309648</v>
       </c>
       <c r="D71">
-        <v>190.9036424349606</v>
+        <v>191.4583087730965</v>
       </c>
       <c r="E71">
-        <v>125.856</v>
+        <v>127.68</v>
       </c>
       <c r="F71">
-        <v>125.856</v>
+        <v>127.68</v>
       </c>
       <c r="G71">
         <v>23.3</v>
@@ -7109,28 +7109,28 @@
         <v>18.8</v>
       </c>
       <c r="M71">
-        <v>11.32704</v>
+        <v>11.4912</v>
       </c>
       <c r="N71">
-        <v>7.47296</v>
+        <v>7.3088</v>
       </c>
       <c r="O71">
-        <v>2.615536</v>
+        <v>2.55808</v>
       </c>
       <c r="P71">
-        <v>4.857424</v>
+        <v>4.750719999999999</v>
       </c>
       <c r="Q71">
-        <v>7.757423999999999</v>
+        <v>7.650719999999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3320446754454114</v>
+        <v>0.3402212976840192</v>
       </c>
       <c r="T71">
-        <v>1.750636801935467</v>
+        <v>1.80064400568225</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.659745176144871</v>
+        <v>1.636034530771373</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1430163893052057</v>
+        <v>0.1427339292223339</v>
       </c>
       <c r="C72">
-        <v>87.07830877309648</v>
+        <v>85.81220764500236</v>
       </c>
       <c r="D72">
-        <v>191.4583087730965</v>
+        <v>192.0162076450024</v>
       </c>
       <c r="E72">
-        <v>127.68</v>
+        <v>129.504</v>
       </c>
       <c r="F72">
-        <v>127.68</v>
+        <v>129.504</v>
       </c>
       <c r="G72">
         <v>23.3</v>
@@ -7191,28 +7191,28 @@
         <v>18.8</v>
       </c>
       <c r="M72">
-        <v>11.4912</v>
+        <v>11.65536</v>
       </c>
       <c r="N72">
-        <v>7.3088</v>
+        <v>7.144639999999999</v>
       </c>
       <c r="O72">
-        <v>2.55808</v>
+        <v>2.500623999999999</v>
       </c>
       <c r="P72">
-        <v>4.750719999999999</v>
+        <v>4.644016</v>
       </c>
       <c r="Q72">
-        <v>7.650719999999998</v>
+        <v>7.544015999999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3402212976840192</v>
+        <v>0.3489618249045998</v>
       </c>
       <c r="T72">
-        <v>1.80064400568225</v>
+        <v>1.854099982101226</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.636034530771373</v>
+        <v>1.612991790901353</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1427339292223339</v>
+        <v>0.1424514691394621</v>
       </c>
       <c r="C73">
-        <v>85.81220764500239</v>
+        <v>84.54936739153322</v>
       </c>
       <c r="D73">
-        <v>192.0162076450024</v>
+        <v>192.5773673915332</v>
       </c>
       <c r="E73">
-        <v>129.504</v>
+        <v>131.328</v>
       </c>
       <c r="F73">
-        <v>129.504</v>
+        <v>131.328</v>
       </c>
       <c r="G73">
         <v>23.3</v>
@@ -7273,28 +7273,28 @@
         <v>18.8</v>
       </c>
       <c r="M73">
-        <v>11.65536</v>
+        <v>11.81952</v>
       </c>
       <c r="N73">
-        <v>7.144640000000003</v>
+        <v>6.98048</v>
       </c>
       <c r="O73">
-        <v>2.500624000000001</v>
+        <v>2.443168</v>
       </c>
       <c r="P73">
-        <v>4.644016000000002</v>
+        <v>4.537312</v>
       </c>
       <c r="Q73">
-        <v>7.544016000000001</v>
+        <v>7.437311999999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3489618249045997</v>
+        <v>0.3583266754980789</v>
       </c>
       <c r="T73">
-        <v>1.854099982101225</v>
+        <v>1.911374242550127</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.612991790901354</v>
+        <v>1.590589127138835</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1424514691394621</v>
+        <v>0.1421690090565903</v>
       </c>
       <c r="C74">
-        <v>84.54936739153322</v>
+        <v>83.28981668581531</v>
       </c>
       <c r="D74">
-        <v>192.5773673915332</v>
+        <v>193.1418166858153</v>
       </c>
       <c r="E74">
-        <v>131.328</v>
+        <v>133.152</v>
       </c>
       <c r="F74">
-        <v>131.328</v>
+        <v>133.152</v>
       </c>
       <c r="G74">
         <v>23.3</v>
@@ -7355,28 +7355,28 @@
         <v>18.8</v>
       </c>
       <c r="M74">
-        <v>11.81952</v>
+        <v>11.98368</v>
       </c>
       <c r="N74">
-        <v>6.98048</v>
+        <v>6.816320000000003</v>
       </c>
       <c r="O74">
-        <v>2.443168</v>
+        <v>2.385712000000001</v>
       </c>
       <c r="P74">
-        <v>4.537312</v>
+        <v>4.430608000000002</v>
       </c>
       <c r="Q74">
-        <v>7.437311999999999</v>
+        <v>7.330608000000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3583266754980789</v>
+        <v>0.3683852187281121</v>
       </c>
       <c r="T74">
-        <v>1.911374242550127</v>
+        <v>1.972891040810059</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.590589127138835</v>
+        <v>1.568800234986248</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1421690090565903</v>
+        <v>0.1418865489737185</v>
       </c>
       <c r="C75">
-        <v>83.28981668581531</v>
+        <v>82.03358453812945</v>
       </c>
       <c r="D75">
-        <v>193.1418166858153</v>
+        <v>193.7095845381294</v>
       </c>
       <c r="E75">
-        <v>133.152</v>
+        <v>134.976</v>
       </c>
       <c r="F75">
-        <v>133.152</v>
+        <v>134.976</v>
       </c>
       <c r="G75">
         <v>23.3</v>
@@ -7437,28 +7437,28 @@
         <v>18.8</v>
       </c>
       <c r="M75">
-        <v>11.98368</v>
+        <v>12.14784</v>
       </c>
       <c r="N75">
-        <v>6.816320000000003</v>
+        <v>6.652160000000002</v>
       </c>
       <c r="O75">
-        <v>2.385712000000001</v>
+        <v>2.328256000000001</v>
       </c>
       <c r="P75">
-        <v>4.430608000000002</v>
+        <v>4.323904000000002</v>
       </c>
       <c r="Q75">
-        <v>7.330608000000001</v>
+        <v>7.223904</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3683852187281121</v>
+        <v>0.3792174960527633</v>
       </c>
       <c r="T75">
-        <v>1.972891040810059</v>
+        <v>2.039139900474601</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.568800234986248</v>
+        <v>1.547600231810758</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1418865489737185</v>
+        <v>0.1416040888908466</v>
       </c>
       <c r="C76">
-        <v>82.03358453812945</v>
+        <v>80.78070030088199</v>
       </c>
       <c r="D76">
-        <v>193.7095845381294</v>
+        <v>194.280700300882</v>
       </c>
       <c r="E76">
-        <v>134.976</v>
+        <v>136.8</v>
       </c>
       <c r="F76">
-        <v>134.976</v>
+        <v>136.8</v>
       </c>
       <c r="G76">
         <v>23.3</v>
@@ -7519,28 +7519,28 @@
         <v>18.8</v>
       </c>
       <c r="M76">
-        <v>12.14784</v>
+        <v>12.312</v>
       </c>
       <c r="N76">
-        <v>6.652160000000002</v>
+        <v>6.488</v>
       </c>
       <c r="O76">
-        <v>2.328256000000001</v>
+        <v>2.270799999999999</v>
       </c>
       <c r="P76">
-        <v>4.323904000000002</v>
+        <v>4.2172</v>
       </c>
       <c r="Q76">
-        <v>7.223904</v>
+        <v>7.117199999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3792174960527633</v>
+        <v>0.3909163555633866</v>
       </c>
       <c r="T76">
-        <v>2.039139900474601</v>
+        <v>2.110688668912306</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.547600231810758</v>
+        <v>1.526965562053281</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1416040888908466</v>
+        <v>0.1413216288079748</v>
       </c>
       <c r="C77">
-        <v>80.78070030088199</v>
+        <v>79.53119367366247</v>
       </c>
       <c r="D77">
-        <v>194.280700300882</v>
+        <v>194.8551936736625</v>
       </c>
       <c r="E77">
-        <v>136.8</v>
+        <v>138.624</v>
       </c>
       <c r="F77">
-        <v>136.8</v>
+        <v>138.624</v>
       </c>
       <c r="G77">
         <v>23.3</v>
@@ -7601,28 +7601,28 @@
         <v>18.8</v>
       </c>
       <c r="M77">
-        <v>12.312</v>
+        <v>12.47616</v>
       </c>
       <c r="N77">
-        <v>6.488</v>
+        <v>6.323840000000002</v>
       </c>
       <c r="O77">
-        <v>2.270799999999999</v>
+        <v>2.213344000000001</v>
       </c>
       <c r="P77">
-        <v>4.2172</v>
+        <v>4.110496000000001</v>
       </c>
       <c r="Q77">
-        <v>7.117199999999999</v>
+        <v>7.010496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3909163555633866</v>
+        <v>0.4035901200332285</v>
       </c>
       <c r="T77">
-        <v>2.110688668912306</v>
+        <v>2.18819983471982</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.526965562053281</v>
+        <v>1.506873909921002</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1413216288079748</v>
+        <v>0.1757353126014296</v>
       </c>
       <c r="C78">
-        <v>79.53119367366247</v>
+        <v>26.09932136902438</v>
       </c>
       <c r="D78">
-        <v>194.8551936736625</v>
+        <v>143.2473213690244</v>
       </c>
       <c r="E78">
-        <v>138.624</v>
+        <v>140.448</v>
       </c>
       <c r="F78">
-        <v>138.624</v>
+        <v>140.448</v>
       </c>
       <c r="G78">
         <v>23.3</v>
@@ -7683,45 +7683,45 @@
         <v>18.8</v>
       </c>
       <c r="M78">
-        <v>12.47616</v>
+        <v>20.6177664</v>
       </c>
       <c r="N78">
-        <v>6.323840000000002</v>
+        <v>-1.817766400000004</v>
       </c>
       <c r="O78">
-        <v>2.213344000000001</v>
+        <v>-0.6362182400000012</v>
       </c>
       <c r="P78">
-        <v>4.110496000000001</v>
+        <v>-1.181548160000002</v>
       </c>
       <c r="Q78">
-        <v>7.010496</v>
+        <v>1.718451839999996</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4035901200332285</v>
+        <v>0.4294516261084276</v>
       </c>
       <c r="T78">
-        <v>2.18819983471982</v>
+        <v>2.34636558651336</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.35</v>
+        <v>0.3191422325941184</v>
       </c>
       <c r="W78">
-        <v>0.0585</v>
+        <v>0.09994992025518343</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.506873909921002</v>
+        <v>0.9118349502689097</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1757353126014296</v>
+        <v>0.1767453126014296</v>
       </c>
       <c r="C79">
-        <v>26.09932136902438</v>
+        <v>23.17043420881663</v>
       </c>
       <c r="D79">
-        <v>143.2473213690244</v>
+        <v>142.1424342088166</v>
       </c>
       <c r="E79">
-        <v>140.448</v>
+        <v>142.272</v>
       </c>
       <c r="F79">
-        <v>140.448</v>
+        <v>142.272</v>
       </c>
       <c r="G79">
         <v>23.3</v>
@@ -7765,37 +7765,37 @@
         <v>18.8</v>
       </c>
       <c r="M79">
-        <v>20.6177664</v>
+        <v>20.88552960000001</v>
       </c>
       <c r="N79">
-        <v>-1.817766400000004</v>
+        <v>-2.085529600000005</v>
       </c>
       <c r="O79">
-        <v>-0.6362182400000012</v>
+        <v>-0.7299353600000016</v>
       </c>
       <c r="P79">
-        <v>-1.181548160000002</v>
+        <v>-1.355594240000003</v>
       </c>
       <c r="Q79">
-        <v>1.718451839999996</v>
+        <v>1.544405759999996</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4294516261084276</v>
+        <v>0.4468903363860834</v>
       </c>
       <c r="T79">
-        <v>2.34636558651336</v>
+        <v>2.453018567718512</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.3191422325941184</v>
+        <v>0.3150506655095784</v>
       </c>
       <c r="W79">
-        <v>0.09994992025518343</v>
+        <v>0.1005505623031939</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9118349502689097</v>
+        <v>0.9001447585987954</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1767453126014296</v>
+        <v>0.1777553126014296</v>
       </c>
       <c r="C80">
-        <v>23.17043420881663</v>
+        <v>20.25846089633214</v>
       </c>
       <c r="D80">
-        <v>142.1424342088166</v>
+        <v>141.0544608963321</v>
       </c>
       <c r="E80">
-        <v>142.272</v>
+        <v>144.096</v>
       </c>
       <c r="F80">
-        <v>142.272</v>
+        <v>144.096</v>
       </c>
       <c r="G80">
         <v>23.3</v>
@@ -7847,37 +7847,37 @@
         <v>18.8</v>
       </c>
       <c r="M80">
-        <v>20.88552960000001</v>
+        <v>21.1532928</v>
       </c>
       <c r="N80">
-        <v>-2.085529600000005</v>
+        <v>-2.353292800000002</v>
       </c>
       <c r="O80">
-        <v>-0.7299353600000016</v>
+        <v>-0.8236524800000007</v>
       </c>
       <c r="P80">
-        <v>-1.355594240000003</v>
+        <v>-1.529640320000001</v>
       </c>
       <c r="Q80">
-        <v>1.544405759999996</v>
+        <v>1.370359679999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4468903363860834</v>
+        <v>0.4659898762139922</v>
       </c>
       <c r="T80">
-        <v>2.453018567718512</v>
+        <v>2.569828975705108</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.3150506655095784</v>
+        <v>0.3110626824018622</v>
       </c>
       <c r="W80">
-        <v>0.1005505623031939</v>
+        <v>0.1011359982234066</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9001447585987954</v>
+        <v>0.8887505211481779</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1777553126014296</v>
+        <v>0.1787653126014296</v>
       </c>
       <c r="C81">
-        <v>20.25846089633214</v>
+        <v>17.36301600053179</v>
       </c>
       <c r="D81">
-        <v>141.0544608963321</v>
+        <v>139.9830160005318</v>
       </c>
       <c r="E81">
-        <v>144.096</v>
+        <v>145.92</v>
       </c>
       <c r="F81">
-        <v>144.096</v>
+        <v>145.92</v>
       </c>
       <c r="G81">
         <v>23.3</v>
@@ -7929,37 +7929,37 @@
         <v>18.8</v>
       </c>
       <c r="M81">
-        <v>21.1532928</v>
+        <v>21.421056</v>
       </c>
       <c r="N81">
-        <v>-2.353292800000002</v>
+        <v>-2.621056000000003</v>
       </c>
       <c r="O81">
-        <v>-0.8236524800000007</v>
+        <v>-0.917369600000001</v>
       </c>
       <c r="P81">
-        <v>-1.529640320000001</v>
+        <v>-1.703686400000002</v>
       </c>
       <c r="Q81">
-        <v>1.370359679999997</v>
+        <v>1.196313599999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4659898762139922</v>
+        <v>0.4869993700246917</v>
       </c>
       <c r="T81">
-        <v>2.569828975705108</v>
+        <v>2.698320424490364</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.3110626824018622</v>
+        <v>0.3071743988718389</v>
       </c>
       <c r="W81">
-        <v>0.1011359982234066</v>
+        <v>0.1017067982456141</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8887505211481779</v>
+        <v>0.8776411396338256</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1787653126014296</v>
+        <v>0.1797753126014296</v>
       </c>
       <c r="C82">
-        <v>17.36301600053179</v>
+        <v>14.483725712976</v>
       </c>
       <c r="D82">
-        <v>139.9830160005318</v>
+        <v>138.927725712976</v>
       </c>
       <c r="E82">
-        <v>145.92</v>
+        <v>147.744</v>
       </c>
       <c r="F82">
-        <v>145.92</v>
+        <v>147.744</v>
       </c>
       <c r="G82">
         <v>23.3</v>
@@ -8011,37 +8011,37 @@
         <v>18.8</v>
       </c>
       <c r="M82">
-        <v>21.421056</v>
+        <v>21.6888192</v>
       </c>
       <c r="N82">
-        <v>-2.621056000000003</v>
+        <v>-2.888819200000004</v>
       </c>
       <c r="O82">
-        <v>-0.917369600000001</v>
+        <v>-1.011086720000001</v>
       </c>
       <c r="P82">
-        <v>-1.703686400000002</v>
+        <v>-1.877732480000003</v>
       </c>
       <c r="Q82">
-        <v>1.196313599999997</v>
+        <v>1.022267519999996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4869993700246917</v>
+        <v>0.5102203894996755</v>
       </c>
       <c r="T82">
-        <v>2.698320424490364</v>
+        <v>2.840337288937225</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.3071743988718389</v>
+        <v>0.303382122342557</v>
       </c>
       <c r="W82">
-        <v>0.1017067982456141</v>
+        <v>0.1022635044401126</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8776411396338256</v>
+        <v>0.8668060638358771</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1797753126014296</v>
+        <v>0.1807853126014295</v>
       </c>
       <c r="C83">
-        <v>14.483725712976</v>
+        <v>11.62022741300606</v>
       </c>
       <c r="D83">
-        <v>138.927725712976</v>
+        <v>137.8882274130061</v>
       </c>
       <c r="E83">
-        <v>147.744</v>
+        <v>149.568</v>
       </c>
       <c r="F83">
-        <v>147.744</v>
+        <v>149.568</v>
       </c>
       <c r="G83">
         <v>23.3</v>
@@ -8093,37 +8093,37 @@
         <v>18.8</v>
       </c>
       <c r="M83">
-        <v>21.6888192</v>
+        <v>21.95658240000001</v>
       </c>
       <c r="N83">
-        <v>-2.888819200000004</v>
+        <v>-3.156582400000005</v>
       </c>
       <c r="O83">
-        <v>-1.011086720000001</v>
+        <v>-1.104803840000002</v>
       </c>
       <c r="P83">
-        <v>-1.877732480000003</v>
+        <v>-2.051778560000003</v>
       </c>
       <c r="Q83">
-        <v>1.022267519999996</v>
+        <v>0.8482214399999952</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5102203894996755</v>
+        <v>0.5360215222496575</v>
       </c>
       <c r="T83">
-        <v>2.840337288937225</v>
+        <v>2.998133804989293</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.303382122342557</v>
+        <v>0.2996823403627697</v>
       </c>
       <c r="W83">
-        <v>0.1022635044401126</v>
+        <v>0.1028066324347454</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8668060638358771</v>
+        <v>0.856235258179342</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1807853126014295</v>
+        <v>0.1817953126014296</v>
       </c>
       <c r="C84">
-        <v>11.62022741300606</v>
+        <v>8.772169252300898</v>
       </c>
       <c r="D84">
-        <v>137.8882274130061</v>
+        <v>136.8641692523009</v>
       </c>
       <c r="E84">
-        <v>149.568</v>
+        <v>151.392</v>
       </c>
       <c r="F84">
-        <v>149.568</v>
+        <v>151.392</v>
       </c>
       <c r="G84">
         <v>23.3</v>
@@ -8175,37 +8175,37 @@
         <v>18.8</v>
       </c>
       <c r="M84">
-        <v>21.95658240000001</v>
+        <v>22.22434560000001</v>
       </c>
       <c r="N84">
-        <v>-3.156582400000005</v>
+        <v>-3.424345600000006</v>
       </c>
       <c r="O84">
-        <v>-1.104803840000002</v>
+        <v>-1.198520960000002</v>
       </c>
       <c r="P84">
-        <v>-2.051778560000003</v>
+        <v>-2.225824640000004</v>
       </c>
       <c r="Q84">
-        <v>0.8482214399999952</v>
+        <v>0.6741753599999947</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5360215222496575</v>
+        <v>0.5648580823819904</v>
       </c>
       <c r="T84">
-        <v>2.998133804989293</v>
+        <v>3.174494617047488</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2996823403627697</v>
+        <v>0.2960717097559893</v>
       </c>
       <c r="W84">
-        <v>0.1028066324347454</v>
+        <v>0.1033366730078208</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.856235258179342</v>
+        <v>0.845919170731398</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1817953126014296</v>
+        <v>0.1828053126014296</v>
       </c>
       <c r="C85">
-        <v>8.772169252300898</v>
+        <v>5.93920975781063</v>
       </c>
       <c r="D85">
-        <v>136.8641692523009</v>
+        <v>135.8552097578106</v>
       </c>
       <c r="E85">
-        <v>151.392</v>
+        <v>153.216</v>
       </c>
       <c r="F85">
-        <v>151.392</v>
+        <v>153.216</v>
       </c>
       <c r="G85">
         <v>23.3</v>
@@ -8257,37 +8257,37 @@
         <v>18.8</v>
       </c>
       <c r="M85">
-        <v>22.22434560000001</v>
+        <v>22.4921088</v>
       </c>
       <c r="N85">
-        <v>-3.424345600000006</v>
+        <v>-3.692108800000003</v>
       </c>
       <c r="O85">
-        <v>-1.198520960000002</v>
+        <v>-1.292238080000001</v>
       </c>
       <c r="P85">
-        <v>-2.225824640000004</v>
+        <v>-2.399870720000002</v>
       </c>
       <c r="Q85">
-        <v>0.6741753599999947</v>
+        <v>0.5001292799999963</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5648580823819904</v>
+        <v>0.5972992125308648</v>
       </c>
       <c r="T85">
-        <v>3.174494617047488</v>
+        <v>3.372900530612956</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2960717097559893</v>
+        <v>0.2925470465446085</v>
       </c>
       <c r="W85">
-        <v>0.1033366730078208</v>
+        <v>0.1038540935672515</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.845919170731398</v>
+        <v>0.8358487044131673</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1828053126014296</v>
+        <v>0.1838153126014296</v>
       </c>
       <c r="C86">
-        <v>5.93920975781063</v>
+        <v>3.121017452123198</v>
       </c>
       <c r="D86">
-        <v>135.8552097578106</v>
+        <v>134.8610174521232</v>
       </c>
       <c r="E86">
-        <v>153.216</v>
+        <v>155.04</v>
       </c>
       <c r="F86">
-        <v>153.216</v>
+        <v>155.04</v>
       </c>
       <c r="G86">
         <v>23.3</v>
@@ -8339,37 +8339,37 @@
         <v>18.8</v>
       </c>
       <c r="M86">
-        <v>22.4921088</v>
+        <v>22.759872</v>
       </c>
       <c r="N86">
-        <v>-3.692108800000003</v>
+        <v>-3.959872000000001</v>
       </c>
       <c r="O86">
-        <v>-1.292238080000001</v>
+        <v>-1.3859552</v>
       </c>
       <c r="P86">
-        <v>-2.399870720000002</v>
+        <v>-2.573916800000001</v>
       </c>
       <c r="Q86">
-        <v>0.5001292799999963</v>
+        <v>0.326083199999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5972992125308646</v>
+        <v>0.6340658266995889</v>
       </c>
       <c r="T86">
-        <v>3.372900530612954</v>
+        <v>3.597760565987151</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2925470465446085</v>
+        <v>0.2891053165852602</v>
       </c>
       <c r="W86">
-        <v>0.1038540935672515</v>
+        <v>0.1043593395252838</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8358487044131673</v>
+        <v>0.8260151902436006</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1838153126014296</v>
+        <v>0.1848253126014296</v>
       </c>
       <c r="C87">
-        <v>3.121017452123198</v>
+        <v>0.3172704903800536</v>
       </c>
       <c r="D87">
-        <v>134.8610174521232</v>
+        <v>133.88127049038</v>
       </c>
       <c r="E87">
-        <v>155.04</v>
+        <v>156.864</v>
       </c>
       <c r="F87">
-        <v>155.04</v>
+        <v>156.864</v>
       </c>
       <c r="G87">
         <v>23.3</v>
@@ -8421,37 +8421,37 @@
         <v>18.8</v>
       </c>
       <c r="M87">
-        <v>22.759872</v>
+        <v>23.0276352</v>
       </c>
       <c r="N87">
-        <v>-3.959872000000001</v>
+        <v>-4.227635200000002</v>
       </c>
       <c r="O87">
-        <v>-1.3859552</v>
+        <v>-1.479672320000001</v>
       </c>
       <c r="P87">
-        <v>-2.573916800000001</v>
+        <v>-2.747962880000001</v>
       </c>
       <c r="Q87">
-        <v>0.326083199999998</v>
+        <v>0.1520371199999975</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6340658266995889</v>
+        <v>0.676084814320988</v>
       </c>
       <c r="T87">
-        <v>3.597760565987151</v>
+        <v>3.854743463557662</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2891053165852602</v>
+        <v>0.2857436268575246</v>
       </c>
       <c r="W87">
-        <v>0.1043593395252838</v>
+        <v>0.1048528355773154</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8260151902436006</v>
+        <v>0.8164103624500704</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1848253126014296</v>
+        <v>0.1858353126014296</v>
       </c>
       <c r="C88">
-        <v>0.3172704903800536</v>
+        <v>-2.472343687096441</v>
       </c>
       <c r="D88">
-        <v>133.88127049038</v>
+        <v>132.9156563129036</v>
       </c>
       <c r="E88">
-        <v>156.864</v>
+        <v>158.688</v>
       </c>
       <c r="F88">
-        <v>156.864</v>
+        <v>158.688</v>
       </c>
       <c r="G88">
         <v>23.3</v>
@@ -8503,37 +8503,37 @@
         <v>18.8</v>
       </c>
       <c r="M88">
-        <v>23.0276352</v>
+        <v>23.2953984</v>
       </c>
       <c r="N88">
-        <v>-4.227635200000002</v>
+        <v>-4.495398400000003</v>
       </c>
       <c r="O88">
-        <v>-1.479672320000001</v>
+        <v>-1.573389440000001</v>
       </c>
       <c r="P88">
-        <v>-2.747962880000001</v>
+        <v>-2.922008960000002</v>
       </c>
       <c r="Q88">
-        <v>0.1520371199999975</v>
+        <v>-0.02200896000000352</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.676084814320988</v>
+        <v>0.7245682615764487</v>
       </c>
       <c r="T88">
-        <v>3.854743463557662</v>
+        <v>4.151262191523636</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2857436268575246</v>
+        <v>0.2824592173534151</v>
       </c>
       <c r="W88">
-        <v>0.1048528355773154</v>
+        <v>0.1053349868925187</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8164103624500704</v>
+        <v>0.8070263352954719</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1858353126014296</v>
+        <v>0.2420965423796661</v>
       </c>
       <c r="C89">
-        <v>-2.472343687096441</v>
+        <v>-42.39175887012011</v>
       </c>
       <c r="D89">
-        <v>132.9156563129036</v>
+        <v>94.82024112987989</v>
       </c>
       <c r="E89">
-        <v>158.688</v>
+        <v>160.512</v>
       </c>
       <c r="F89">
-        <v>158.688</v>
+        <v>160.512</v>
       </c>
       <c r="G89">
         <v>23.3</v>
@@ -8585,45 +8585,45 @@
         <v>18.8</v>
       </c>
       <c r="M89">
-        <v>23.2953984</v>
+        <v>32.2308096</v>
       </c>
       <c r="N89">
-        <v>-4.495398400000003</v>
+        <v>-13.4308096</v>
       </c>
       <c r="O89">
-        <v>-1.573389440000001</v>
+        <v>-4.70078336</v>
       </c>
       <c r="P89">
-        <v>-2.922008960000002</v>
+        <v>-8.730026240000001</v>
       </c>
       <c r="Q89">
-        <v>-0.02200896000000352</v>
+        <v>-5.830026240000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7245682615764487</v>
+        <v>0.8455591981931241</v>
       </c>
       <c r="T89">
-        <v>4.151262191523636</v>
+        <v>4.891227698348188</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.2824592173534151</v>
+        <v>0.2041524889278611</v>
       </c>
       <c r="W89">
-        <v>0.1053349868925187</v>
+        <v>0.1598061802232855</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8070263352954719</v>
+        <v>0.5832928255081746</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2420965423796661</v>
+        <v>0.2436465423796661</v>
       </c>
       <c r="C90">
-        <v>-42.39175887012011</v>
+        <v>-44.9586142770611</v>
       </c>
       <c r="D90">
-        <v>94.82024112987989</v>
+        <v>94.07738572293891</v>
       </c>
       <c r="E90">
-        <v>160.512</v>
+        <v>162.336</v>
       </c>
       <c r="F90">
-        <v>160.512</v>
+        <v>162.336</v>
       </c>
       <c r="G90">
         <v>23.3</v>
@@ -8667,37 +8667,37 @@
         <v>18.8</v>
       </c>
       <c r="M90">
-        <v>32.2308096</v>
+        <v>32.5970688</v>
       </c>
       <c r="N90">
-        <v>-13.4308096</v>
+        <v>-13.7970688</v>
       </c>
       <c r="O90">
-        <v>-4.70078336</v>
+        <v>-4.82897408</v>
       </c>
       <c r="P90">
-        <v>-8.730026240000001</v>
+        <v>-8.968094720000002</v>
       </c>
       <c r="Q90">
-        <v>-5.830026240000002</v>
+        <v>-6.068094720000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8455591981931241</v>
+        <v>0.9182645798470445</v>
       </c>
       <c r="T90">
-        <v>4.891227698348188</v>
+        <v>5.335884761834387</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.2041524889278611</v>
+        <v>0.2018586407376604</v>
       </c>
       <c r="W90">
-        <v>0.1598061802232855</v>
+        <v>0.1602667849398778</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5832928255081746</v>
+        <v>0.5767389735361726</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2436465423796661</v>
+        <v>0.2451965423796661</v>
       </c>
       <c r="C91">
-        <v>-44.9586142770611</v>
+        <v>-47.51392057821499</v>
       </c>
       <c r="D91">
-        <v>94.07738572293891</v>
+        <v>93.34607942178501</v>
       </c>
       <c r="E91">
-        <v>162.336</v>
+        <v>164.16</v>
       </c>
       <c r="F91">
-        <v>162.336</v>
+        <v>164.16</v>
       </c>
       <c r="G91">
         <v>23.3</v>
@@ -8749,37 +8749,37 @@
         <v>18.8</v>
       </c>
       <c r="M91">
-        <v>32.5970688</v>
+        <v>32.963328</v>
       </c>
       <c r="N91">
-        <v>-13.7970688</v>
+        <v>-14.163328</v>
       </c>
       <c r="O91">
-        <v>-4.82897408</v>
+        <v>-4.957164799999998</v>
       </c>
       <c r="P91">
-        <v>-8.968094720000002</v>
+        <v>-9.206163199999999</v>
       </c>
       <c r="Q91">
-        <v>-6.068094720000003</v>
+        <v>-6.3061632</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9182645798470445</v>
+        <v>1.005511037831749</v>
       </c>
       <c r="T91">
-        <v>5.335884761834387</v>
+        <v>5.869473238017825</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.2018586407376604</v>
+        <v>0.1996157669516865</v>
       </c>
       <c r="W91">
-        <v>0.1602667849398778</v>
+        <v>0.1607171539961014</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5767389735361726</v>
+        <v>0.5703307627191041</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2451965423796661</v>
+        <v>0.2467465423796661</v>
       </c>
       <c r="C92">
-        <v>-47.51392057821499</v>
+        <v>-50.05794502546526</v>
       </c>
       <c r="D92">
-        <v>93.34607942178501</v>
+        <v>92.62605497453475</v>
       </c>
       <c r="E92">
-        <v>164.16</v>
+        <v>165.984</v>
       </c>
       <c r="F92">
-        <v>164.16</v>
+        <v>165.984</v>
       </c>
       <c r="G92">
         <v>23.3</v>
@@ -8831,37 +8831,37 @@
         <v>18.8</v>
       </c>
       <c r="M92">
-        <v>32.963328</v>
+        <v>33.32958720000001</v>
       </c>
       <c r="N92">
-        <v>-14.163328</v>
+        <v>-14.52958720000001</v>
       </c>
       <c r="O92">
-        <v>-4.957164799999998</v>
+        <v>-5.085355520000001</v>
       </c>
       <c r="P92">
-        <v>-9.206163199999999</v>
+        <v>-9.444231680000005</v>
       </c>
       <c r="Q92">
-        <v>-6.3061632</v>
+        <v>-6.544231680000006</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.005511037831749</v>
+        <v>1.112145597590832</v>
       </c>
       <c r="T92">
-        <v>5.869473238017825</v>
+        <v>6.521636931130918</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1996157669516865</v>
+        <v>0.1974221870950745</v>
       </c>
       <c r="W92">
-        <v>0.1607171539961014</v>
+        <v>0.161157624831309</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5703307627191041</v>
+        <v>0.5640633917002127</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2467465423796661</v>
+        <v>0.2482965423796661</v>
       </c>
       <c r="C93">
-        <v>-50.05794502546526</v>
+        <v>-52.59094668802872</v>
       </c>
       <c r="D93">
-        <v>92.62605497453475</v>
+        <v>91.9170533119713</v>
       </c>
       <c r="E93">
-        <v>165.984</v>
+        <v>167.808</v>
       </c>
       <c r="F93">
-        <v>165.984</v>
+        <v>167.808</v>
       </c>
       <c r="G93">
         <v>23.3</v>
@@ -8913,37 +8913,37 @@
         <v>18.8</v>
       </c>
       <c r="M93">
-        <v>33.32958720000001</v>
+        <v>33.69584640000001</v>
       </c>
       <c r="N93">
-        <v>-14.52958720000001</v>
+        <v>-14.89584640000001</v>
       </c>
       <c r="O93">
-        <v>-5.085355520000001</v>
+        <v>-5.213546240000002</v>
       </c>
       <c r="P93">
-        <v>-9.444231680000005</v>
+        <v>-9.682300160000004</v>
       </c>
       <c r="Q93">
-        <v>-6.544231680000006</v>
+        <v>-6.782300160000005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.112145597590832</v>
+        <v>1.245438797289687</v>
       </c>
       <c r="T93">
-        <v>6.521636931130918</v>
+        <v>7.336841547522286</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1974221870950745</v>
+        <v>0.1952762937570845</v>
       </c>
       <c r="W93">
-        <v>0.161157624831309</v>
+        <v>0.1615885202135774</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5640633917002127</v>
+        <v>0.5579322678773844</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2482965423796661</v>
+        <v>0.2498465423796661</v>
       </c>
       <c r="C94">
-        <v>-52.59094668802872</v>
+        <v>-55.11317676324586</v>
       </c>
       <c r="D94">
-        <v>91.9170533119713</v>
+        <v>91.21882323675415</v>
       </c>
       <c r="E94">
-        <v>167.808</v>
+        <v>169.632</v>
       </c>
       <c r="F94">
-        <v>167.808</v>
+        <v>169.632</v>
       </c>
       <c r="G94">
         <v>23.3</v>
@@ -8995,37 +8995,37 @@
         <v>18.8</v>
       </c>
       <c r="M94">
-        <v>33.69584640000001</v>
+        <v>34.0621056</v>
       </c>
       <c r="N94">
-        <v>-14.89584640000001</v>
+        <v>-15.2621056</v>
       </c>
       <c r="O94">
-        <v>-5.213546240000002</v>
+        <v>-5.34173696</v>
       </c>
       <c r="P94">
-        <v>-9.682300160000004</v>
+        <v>-9.920368640000001</v>
       </c>
       <c r="Q94">
-        <v>-6.782300160000005</v>
+        <v>-7.020368640000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.245438797289687</v>
+        <v>1.416815768331071</v>
       </c>
       <c r="T94">
-        <v>7.336841547522286</v>
+        <v>8.384961768596899</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1952762937570845</v>
+        <v>0.1931765486629223</v>
       </c>
       <c r="W94">
-        <v>0.1615885202135774</v>
+        <v>0.1620101490284852</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5579322678773844</v>
+        <v>0.5519329961797781</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2498465423796661</v>
+        <v>0.2513965423796661</v>
       </c>
       <c r="C95">
-        <v>-55.11317676324586</v>
+        <v>-57.62487887331285</v>
       </c>
       <c r="D95">
-        <v>91.21882323675415</v>
+        <v>90.53112112668717</v>
       </c>
       <c r="E95">
-        <v>169.632</v>
+        <v>171.456</v>
       </c>
       <c r="F95">
-        <v>169.632</v>
+        <v>171.456</v>
       </c>
       <c r="G95">
         <v>23.3</v>
@@ -9077,37 +9077,37 @@
         <v>18.8</v>
       </c>
       <c r="M95">
-        <v>34.0621056</v>
+        <v>34.4283648</v>
       </c>
       <c r="N95">
-        <v>-15.2621056</v>
+        <v>-15.6283648</v>
       </c>
       <c r="O95">
-        <v>-5.34173696</v>
+        <v>-5.469927680000001</v>
       </c>
       <c r="P95">
-        <v>-9.920368640000001</v>
+        <v>-10.15843712</v>
       </c>
       <c r="Q95">
-        <v>-7.020368640000003</v>
+        <v>-7.258437120000004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.416815768331071</v>
+        <v>1.645318396386249</v>
       </c>
       <c r="T95">
-        <v>8.384961768596899</v>
+        <v>9.782455396696383</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1931765486629223</v>
+        <v>0.1911214789962955</v>
       </c>
       <c r="W95">
-        <v>0.1620101490284852</v>
+        <v>0.1624228070175439</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5519329961797781</v>
+        <v>0.5460613685608443</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2513965423796661</v>
+        <v>0.2529465423796662</v>
       </c>
       <c r="C96">
-        <v>-57.62487887331285</v>
+        <v>-60.1262893486911</v>
       </c>
       <c r="D96">
-        <v>90.53112112668717</v>
+        <v>89.85371065130893</v>
       </c>
       <c r="E96">
-        <v>171.456</v>
+        <v>173.28</v>
       </c>
       <c r="F96">
-        <v>171.456</v>
+        <v>173.28</v>
       </c>
       <c r="G96">
         <v>23.3</v>
@@ -9159,37 +9159,37 @@
         <v>18.8</v>
       </c>
       <c r="M96">
-        <v>34.4283648</v>
+        <v>34.79462400000001</v>
       </c>
       <c r="N96">
-        <v>-15.6283648</v>
+        <v>-15.99462400000001</v>
       </c>
       <c r="O96">
-        <v>-5.469927680000001</v>
+        <v>-5.598118400000001</v>
       </c>
       <c r="P96">
-        <v>-10.15843712</v>
+        <v>-10.3965056</v>
       </c>
       <c r="Q96">
-        <v>-7.258437120000004</v>
+        <v>-7.496505600000006</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.645318396386249</v>
+        <v>1.965222075663501</v>
       </c>
       <c r="T96">
-        <v>9.782455396696383</v>
+        <v>11.73894647603567</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1911214789962955</v>
+        <v>0.1891096739542292</v>
       </c>
       <c r="W96">
-        <v>0.1624228070175439</v>
+        <v>0.1628267774699908</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5460613685608443</v>
+        <v>0.5403133541549406</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2529465423796662</v>
+        <v>0.2544965423796661</v>
       </c>
       <c r="C97">
-        <v>-60.1262893486911</v>
+        <v>-62.6176374988878</v>
       </c>
       <c r="D97">
-        <v>89.85371065130893</v>
+        <v>89.18636250111221</v>
       </c>
       <c r="E97">
-        <v>173.28</v>
+        <v>175.104</v>
       </c>
       <c r="F97">
-        <v>173.28</v>
+        <v>175.104</v>
       </c>
       <c r="G97">
         <v>23.3</v>
@@ -9241,37 +9241,37 @@
         <v>18.8</v>
       </c>
       <c r="M97">
-        <v>34.79462400000001</v>
+        <v>35.1608832</v>
       </c>
       <c r="N97">
-        <v>-15.99462400000001</v>
+        <v>-16.3608832</v>
       </c>
       <c r="O97">
-        <v>-5.598118400000001</v>
+        <v>-5.72630912</v>
       </c>
       <c r="P97">
-        <v>-10.3965056</v>
+        <v>-10.63457408</v>
       </c>
       <c r="Q97">
-        <v>-7.496505600000006</v>
+        <v>-7.734574080000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.965222075663501</v>
+        <v>2.445077594579376</v>
       </c>
       <c r="T97">
-        <v>11.73894647603567</v>
+        <v>14.67368309504459</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1891096739542292</v>
+        <v>0.187139781517206</v>
       </c>
       <c r="W97">
-        <v>0.1628267774699908</v>
+        <v>0.163222331871345</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5403133541549406</v>
+        <v>0.5346850900491601</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2544965423796661</v>
+        <v>0.2560465423796661</v>
       </c>
       <c r="C98">
-        <v>-62.61763749888777</v>
+        <v>-65.09914587125897</v>
       </c>
       <c r="D98">
-        <v>89.18636250111221</v>
+        <v>88.52885412874103</v>
       </c>
       <c r="E98">
-        <v>175.104</v>
+        <v>176.928</v>
       </c>
       <c r="F98">
-        <v>175.104</v>
+        <v>176.928</v>
       </c>
       <c r="G98">
         <v>23.3</v>
@@ -9323,37 +9323,37 @@
         <v>18.8</v>
       </c>
       <c r="M98">
-        <v>35.1608832</v>
+        <v>35.5271424</v>
       </c>
       <c r="N98">
-        <v>-16.3608832</v>
+        <v>-16.7271424</v>
       </c>
       <c r="O98">
-        <v>-5.72630912</v>
+        <v>-5.85449984</v>
       </c>
       <c r="P98">
-        <v>-10.63457408</v>
+        <v>-10.87264256</v>
       </c>
       <c r="Q98">
-        <v>-7.734574080000002</v>
+        <v>-7.972642560000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.44507759457937</v>
+        <v>3.244836792772494</v>
       </c>
       <c r="T98">
-        <v>14.67368309504455</v>
+        <v>19.56491079339274</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.187139781517206</v>
+        <v>0.1852105054190905</v>
       </c>
       <c r="W98">
-        <v>0.163222331871345</v>
+        <v>0.1636097305118466</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5346850900491601</v>
+        <v>0.5291728726259728</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2560465423796661</v>
+        <v>0.2575965423796661</v>
       </c>
       <c r="C99">
-        <v>-65.09914587125897</v>
+        <v>-67.5710304984479</v>
       </c>
       <c r="D99">
-        <v>88.52885412874103</v>
+        <v>87.88096950155212</v>
       </c>
       <c r="E99">
-        <v>176.928</v>
+        <v>178.752</v>
       </c>
       <c r="F99">
-        <v>176.928</v>
+        <v>178.752</v>
       </c>
       <c r="G99">
         <v>23.3</v>
@@ -9405,37 +9405,37 @@
         <v>18.8</v>
       </c>
       <c r="M99">
-        <v>35.5271424</v>
+        <v>35.8934016</v>
       </c>
       <c r="N99">
-        <v>-16.7271424</v>
+        <v>-17.0934016</v>
       </c>
       <c r="O99">
-        <v>-5.85449984</v>
+        <v>-5.982690560000001</v>
       </c>
       <c r="P99">
-        <v>-10.87264256</v>
+        <v>-11.11071104</v>
       </c>
       <c r="Q99">
-        <v>-7.972642560000004</v>
+        <v>-8.210711040000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.244836792772494</v>
+        <v>4.84435518915874</v>
       </c>
       <c r="T99">
-        <v>19.56491079339274</v>
+        <v>29.3473661900891</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1852105054190905</v>
+        <v>0.1833206023025692</v>
       </c>
       <c r="W99">
-        <v>0.1636097305118466</v>
+        <v>0.1639892230576441</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5291728726259728</v>
+        <v>0.5237731494359119</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2575965423796661</v>
+        <v>0.2591465423796661</v>
       </c>
       <c r="C100">
-        <v>-67.5710304984479</v>
+        <v>-70.0335011350378</v>
       </c>
       <c r="D100">
-        <v>87.88096950155212</v>
+        <v>87.2424988649622</v>
       </c>
       <c r="E100">
-        <v>178.752</v>
+        <v>180.576</v>
       </c>
       <c r="F100">
-        <v>178.752</v>
+        <v>180.576</v>
       </c>
       <c r="G100">
         <v>23.3</v>
@@ -9487,37 +9487,37 @@
         <v>18.8</v>
       </c>
       <c r="M100">
-        <v>35.8934016</v>
+        <v>36.2596608</v>
       </c>
       <c r="N100">
-        <v>-17.0934016</v>
+        <v>-17.4596608</v>
       </c>
       <c r="O100">
-        <v>-5.982690560000001</v>
+        <v>-6.110881279999999</v>
       </c>
       <c r="P100">
-        <v>-11.11071104</v>
+        <v>-11.34877952</v>
       </c>
       <c r="Q100">
-        <v>-8.210711040000003</v>
+        <v>-8.44877952</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.84435518915874</v>
+        <v>9.642910378317479</v>
       </c>
       <c r="T100">
-        <v>29.3473661900891</v>
+        <v>58.69473238017819</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1833206023025692</v>
+        <v>0.1814688790469877</v>
       </c>
       <c r="W100">
-        <v>0.1639892230576441</v>
+        <v>0.1643610490873649</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5237731494359119</v>
+        <v>0.518482511562822</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2591465423796661</v>
-      </c>
-      <c r="C101">
-        <v>-70.0335011350378</v>
-      </c>
-      <c r="D101">
-        <v>87.2424988649622</v>
-      </c>
-      <c r="E101">
-        <v>180.576</v>
-      </c>
-      <c r="F101">
-        <v>180.576</v>
-      </c>
-      <c r="G101">
-        <v>23.3</v>
-      </c>
-      <c r="H101">
-        <v>182.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>21.7</v>
-      </c>
-      <c r="K101">
-        <v>2.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>18.8</v>
-      </c>
-      <c r="M101">
-        <v>36.2596608</v>
-      </c>
-      <c r="N101">
-        <v>-17.4596608</v>
-      </c>
-      <c r="O101">
-        <v>-6.110881279999999</v>
-      </c>
-      <c r="P101">
-        <v>-11.34877952</v>
-      </c>
-      <c r="Q101">
-        <v>-8.44877952</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.642910378317479</v>
-      </c>
-      <c r="T101">
-        <v>58.69473238017819</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1814688790469877</v>
-      </c>
-      <c r="W101">
-        <v>0.1643610490873649</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.518482511562822</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
